--- a/result_analysis/analysis.xlsx
+++ b/result_analysis/analysis.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tintin/Desktop/Projects/credit_risk_model/result_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F000B51-50AC-804E-9DAC-69B67AD6943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB81ED7-E03B-4143-B776-B8A16D9A4D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{61FC1A9A-6CB0-D841-9DA7-4D6ECF9C438C}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{61FC1A9A-6CB0-D841-9DA7-4D6ECF9C438C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="raw_data" sheetId="1" r:id="rId1"/>
+    <sheet name="cleaned_data" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="results" localSheetId="0">Sheet1!$B$1:$E$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">raw_data!$A$1:$E$1</definedName>
+    <definedName name="results" localSheetId="0">raw_data!$B$1:$E$401</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -53,15 +55,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>actual</t>
-  </si>
-  <si>
-    <t>prob_0</t>
-  </si>
-  <si>
-    <t>prob_1</t>
   </si>
   <si>
     <t>predicted</t>
@@ -69,13 +65,34 @@
   <si>
     <t>index</t>
   </si>
+  <si>
+    <t>Probability_Safe</t>
+  </si>
+  <si>
+    <t>Proabability_Default</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -100,16 +117,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -124,6 +170,23 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results" connectionId="1" xr16:uid="{9CD43543-71DA-BE45-BDDA-81577C54F7A4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}" name="Table1" displayName="Table1" ref="A1:E401" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E401" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E401">
+    <sortCondition descending="1" ref="C1:C1048576"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A33D2E8F-C4FE-744C-B6EA-6D08D082939C}" name="index"/>
+    <tableColumn id="2" xr3:uid="{B6ED8025-A452-0545-83F5-078527E9E23D}" name="actual"/>
+    <tableColumn id="3" xr3:uid="{482B43F2-766E-4344-A44D-179FE0BFAA6E}" name="Probability_Safe" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{797E6CBE-CC91-DD44-BA30-CDAD50AEEDE6}" name="Proabability_Default" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{8F649A08-FC6F-404F-ADA2-2B66671FF421}" name="predicted"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,26 +490,27 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -7652,4 +7716,6838 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6AB79F-0D4E-3442-89AE-0F2C22D8D512}">
+  <dimension ref="A1:E401"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="4" width="20.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>384</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.82503400713532005</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.17496599286467901</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>330</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.82158174384212701</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.17841825615787199</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>341</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.80794744749740299</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.19205255250259601</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.77347535673464496</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.22652464326535399</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>52</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.76692651002603096</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.23307348997396801</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>356</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.76663505665523601</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.23336494334476299</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>106</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.765516263403206</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.234483736596793</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>105</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.76031332844253696</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.23968667155746201</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>141</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.76025575181913996</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.23974424818085899</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>136</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.75702518889234005</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.24297481110765901</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>234</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.75672824354326695</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.24327175645673199</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>181</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.75312170932141098</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.24687829067858799</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.74606387404385499</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.25393612595614401</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>318</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.74440235035125202</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.25559764964874698</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>264</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.72339284582967001</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.27660715417032899</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>368</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.72274873403993301</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.277251265960066</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>127</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.720072153616232</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.279927846383767</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.71976402939073203</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.28023597060926703</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>62</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.70994477938834299</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.29005522061165601</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>133</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.70820036920719098</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.29179963079280802</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>246</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.70668992579615797</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.29331007420384198</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>51</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.70495768466030795</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.295042315339691</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>67</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.69867962252586402</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.30132037747413498</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>374</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.69788228181596701</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.30211771818403199</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>151</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.69769425226210302</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.30230574773789598</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>344</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.69665244823072903</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.30334755176926997</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>175</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.69629452308208795</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.303705476917911</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>179</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.69551089254609799</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.30448910745390101</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>164</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.69092089518739497</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.30907910481260398</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>46</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.68912603776733605</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.310873962232663</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.68414390250879997</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.31585609749119897</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.68039890368967304</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.31960109631032602</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>77</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.67682613641658396</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.32317386358341499</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>57</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.66865401022957904</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.33134598977042001</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>143</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.66650289179223299</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.33349710820776601</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>64</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.65975580911763299</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.34024419088236602</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>149</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.65950496640613998</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.34049503359385902</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>273</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.65647768033153198</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.34352231966846702</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>288</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.65339672797952197</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.34660327202047703</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>307</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.65194753076888401</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.34805246923111499</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>21</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.64118633775858003</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.35881366224141897</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>267</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.63542216780036598</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.36457783219963302</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.62976815584399404</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.37023184415600502</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>389</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.62624388458754698</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.37375611541245202</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>41</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.62488082507515696</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.37511917492484198</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>171</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.61914961331369101</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0.380850386686308</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>329</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.61796354702745404</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0.38203645297254502</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>97</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.61727408366533698</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0.38272591633466202</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>399</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.61225365250215802</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0.38774634749784098</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>161</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.60562783860859004</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0.39437216139140902</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>263</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.60165637151364404</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0.39834362848635502</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>233</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.59835038011520503</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0.40164961988479497</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>365</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.59699831635998601</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0.40300168364001299</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>269</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.58857271255664101</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.41142728744335799</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>32</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.58764472458003303</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0.41235527541996603</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.58668245911982098</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0.41331754088017802</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>211</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.58372538605829905</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0.41627461394170001</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>282</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.581315980488193</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0.418684019511806</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>327</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.57363821820748795</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0.426361781792512</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>131</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.57297449365773701</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0.42702550634226299</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>177</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0.57251257493956198</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0.42748742506043702</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>291</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63" s="2">
+        <v>0.57189629354016902</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0.42810370645982998</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>22</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64" s="2">
+        <v>0.569553228035239</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0.43044677196476</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>155</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.56842974929308798</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.43157025070691102</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0.56585200155120496</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.43414799844879398</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>157</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.56409911280301706</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.435900887196982</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>120</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.56240842927651002</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.43759157072348898</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>272</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.55755742041737399</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.44244257958262501</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>90</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.55746729042809795</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.442532709571901</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>195</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.55408984271941697</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.44591015728058198</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>15</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.55402137857425005</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0.44597862142574901</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>94</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.55328556234154003</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0.44671443765845897</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>36</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0.54962624187008802</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0.45037375812991098</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>347</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0.549494286802094</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0.450505713197905</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>31</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0.54661961512289503</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0.45338038487710403</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>237</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" s="2">
+        <v>0.54223416007430103</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0.45776583992569803</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>53</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0.53799642141559001</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0.46200357858440899</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>156</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79" s="2">
+        <v>0.53400946481075595</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0.46599053518924299</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>289</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0.53240914966711295</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.467590850332886</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>385</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0.52552482761053498</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0.47447517238946402</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>159</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0.52415741302443397</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0.47584258697556497</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>162</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0.51899216178449803</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0.48100783821550103</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>363</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84" s="2">
+        <v>0.51524994677824398</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0.48475005322175502</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" s="2">
+        <v>0.51442454871687004</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0.48557545128312901</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>108</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0.51381634828274703</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0.48618365171725197</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>355</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0.51089785586324499</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0.48910214413675401</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>376</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" s="2">
+        <v>0.50713081304568297</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0.49286918695431597</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>322</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89" s="2">
+        <v>0.50677657054531899</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.49322342945468001</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>210</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90" s="2">
+        <v>0.50387210407711203</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.49612789592288797</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>29</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" s="2">
+        <v>0.50151153933103498</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.49848846066896402</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>28</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" s="2">
+        <v>0.50028208072713698</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.49971791927286202</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>196</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" s="2">
+        <v>0.49996779850686501</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.50003220149313399</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>18</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94" s="2">
+        <v>0.49893371692821997</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.50106628307177903</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>280</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0.492064556855701</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.50793544314429795</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>243</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" s="2">
+        <v>0.49115954554803998</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0.50884045445195902</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>98</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97" s="2">
+        <v>0.48924707307172799</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0.51075292692827101</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>139</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0.48579403022614398</v>
+      </c>
+      <c r="D98" s="2">
+        <v>0.51420596977385502</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>10</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" s="2">
+        <v>0.484814554431381</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0.51518544556861801</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>178</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" s="2">
+        <v>0.48293966373122399</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0.51706033626877501</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>239</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101" s="2">
+        <v>0.479211650366479</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0.52078834963352005</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>0</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2">
+        <v>0.47917879496022198</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0.52082120503977702</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>279</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0.47817569459750597</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0.52182430540249303</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>251</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104" s="2">
+        <v>0.47736289163957002</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0.52263710836042898</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>184</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0.47569637223121702</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0.52430362776878203</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>360</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0.47309116483942099</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0.52690883516057796</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>180</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0.46684649874114398</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0.53315350125885497</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>343</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0.464936477228028</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0.535063522771971</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>236</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0.46355419166759299</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0.53644580833240596</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>397</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0.46133435036995002</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0.53866564963004904</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>252</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0.460815389856161</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0.53918461014383801</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>315</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0.460246149425933</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0.539753850574066</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>313</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0.46016692119865099</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0.53983307880134801</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>342</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114" s="2">
+        <v>0.45837929244292203</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0.54162070755707703</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>220</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0.45580682132009398</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0.54419317867990502</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>265</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" s="2">
+        <v>0.45461313661081898</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0.54538686338917997</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>82</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" s="2">
+        <v>0.45414094314373399</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0.54585905685626501</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>390</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" s="2">
+        <v>0.44999501854929402</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0.55000498145070598</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>163</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0.44501333059346398</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0.55498666940653496</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>334</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120" s="2">
+        <v>0.443993155584614</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0.55600684441538495</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>328</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121" s="2">
+        <v>0.43757778714511097</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0.56242221285488803</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>326</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" s="2">
+        <v>0.43517222180315002</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0.56482777819684904</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>24</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2">
+        <v>0.43409471053679699</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0.56590528946320195</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>350</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124" s="2">
+        <v>0.43237789482669697</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0.56762210517330203</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>63</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125" s="2">
+        <v>0.431198767000112</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0.56880123299988705</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>339</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2">
+        <v>0.42802902753623201</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0.57197097246376705</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>319</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0.42105988515153397</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0.57894011484846497</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>20</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.420856120362121</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0.57914387963787795</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>122</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.42084065872179399</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0.57915934127820501</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>387</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.42061007803986</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0.57938992196013905</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>316</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.41958265785267901</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0.58041734214731999</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>188</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.419284441852046</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0.58071555814795295</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>227</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.41692655978883802</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0.58307344021116103</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>186</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.41506780110979002</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0.58493219889020898</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>26</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.41040746297325498</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0.58959253702674397</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>361</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.41009599632030103</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0.58990400367969797</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>312</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.40983085955818799</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0.59016914044181101</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>300</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.40703652695507297</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0.59296347304492603</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>78</v>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.40677009417979199</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0.59322990582020696</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>277</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.406092544147795</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0.59390745585220395</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>96</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.404889617997508</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0.595110382002491</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>299</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.40467611180049401</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0.59532388819950499</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>256</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.403148640243434</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0.596851359756565</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>49</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.40276566195411301</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0.59723433804588599</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>386</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.39290176906390001</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0.60709823093609905</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>146</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.39271216693817601</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0.60728783306182299</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>154</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.38965652511280502</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0.61034347488719398</v>
+      </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>40</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.38915530580473101</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0.61084469419526799</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>86</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.38874413422845</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0.611255865771549</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>370</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.38412705961094001</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0.61587294038905904</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>253</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.38408044177670497</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0.61591955822329403</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>231</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.38145424209809498</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0.61854575790190403</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>103</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.37900338060171501</v>
+      </c>
+      <c r="D153" s="2">
+        <v>0.62099661939828399</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>119</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.37614659168917403</v>
+      </c>
+      <c r="D154" s="2">
+        <v>0.62385340831082503</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>19</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.37533076811223998</v>
+      </c>
+      <c r="D155" s="2">
+        <v>0.62466923188775902</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>209</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.37480688782848398</v>
+      </c>
+      <c r="D156" s="2">
+        <v>0.62519311217151496</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>323</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.37448994398639801</v>
+      </c>
+      <c r="D157" s="2">
+        <v>0.62551005601360199</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>2</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.37313482853214602</v>
+      </c>
+      <c r="D158" s="2">
+        <v>0.62686517146785303</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>214</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.37246639873509901</v>
+      </c>
+      <c r="D159" s="2">
+        <v>0.62753360126489999</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>174</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.36717398424111303</v>
+      </c>
+      <c r="D160" s="2">
+        <v>0.63282601575888597</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>79</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.36519773535169497</v>
+      </c>
+      <c r="D161" s="2">
+        <v>0.63480226464830403</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>383</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.36242433927902501</v>
+      </c>
+      <c r="D162" s="2">
+        <v>0.63757566072097405</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>206</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163" s="2">
+        <v>0.36187059885015399</v>
+      </c>
+      <c r="D163" s="2">
+        <v>0.63812940114984495</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>381</v>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164" s="2">
+        <v>0.360801501137202</v>
+      </c>
+      <c r="D164" s="2">
+        <v>0.639198498862797</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>129</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165" s="2">
+        <v>0.360303582094679</v>
+      </c>
+      <c r="D165" s="2">
+        <v>0.63969641790532095</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>198</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166" s="2">
+        <v>0.36020230592508801</v>
+      </c>
+      <c r="D166" s="2">
+        <v>0.63979769407491105</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>258</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167" s="2">
+        <v>0.35882112486155499</v>
+      </c>
+      <c r="D167" s="2">
+        <v>0.64117887513844496</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>138</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168" s="2">
+        <v>0.35504389074395398</v>
+      </c>
+      <c r="D168" s="2">
+        <v>0.64495610925604496</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>297</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169" s="2">
+        <v>0.35419913857142499</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0.64580086142857396</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>111</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170" s="2">
+        <v>0.351634587736596</v>
+      </c>
+      <c r="D170" s="2">
+        <v>0.64836541226340305</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>102</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171" s="2">
+        <v>0.35022183900291098</v>
+      </c>
+      <c r="D171" s="2">
+        <v>0.64977816099708796</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>366</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172" s="2">
+        <v>0.34966680554516899</v>
+      </c>
+      <c r="D172" s="2">
+        <v>0.65033319445482995</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>199</v>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+      <c r="C173" s="2">
+        <v>0.34404270866895897</v>
+      </c>
+      <c r="D173" s="2">
+        <v>0.65595729133103997</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>259</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174" s="2">
+        <v>0.34179201865543501</v>
+      </c>
+      <c r="D174" s="2">
+        <v>0.65820798134456404</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>202</v>
+      </c>
+      <c r="B175">
+        <v>1</v>
+      </c>
+      <c r="C175" s="2">
+        <v>0.34036807528809898</v>
+      </c>
+      <c r="D175" s="2">
+        <v>0.65963192471190002</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>261</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176" s="2">
+        <v>0.33953936742927499</v>
+      </c>
+      <c r="D176" s="2">
+        <v>0.66046063257072396</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>320</v>
+      </c>
+      <c r="B177">
+        <v>1</v>
+      </c>
+      <c r="C177" s="2">
+        <v>0.33683371706656301</v>
+      </c>
+      <c r="D177" s="2">
+        <v>0.66316628293343605</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>69</v>
+      </c>
+      <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178" s="2">
+        <v>0.33531155423528902</v>
+      </c>
+      <c r="D178" s="2">
+        <v>0.66468844576470998</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>217</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179" s="2">
+        <v>0.33397925673477202</v>
+      </c>
+      <c r="D179" s="2">
+        <v>0.66602074326522798</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>121</v>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180" s="2">
+        <v>0.33316374142997002</v>
+      </c>
+      <c r="D180" s="2">
+        <v>0.66683625857002904</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>169</v>
+      </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="C181" s="2">
+        <v>0.33290418266782101</v>
+      </c>
+      <c r="D181" s="2">
+        <v>0.66709581733217804</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>74</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182" s="2">
+        <v>0.33252591512111801</v>
+      </c>
+      <c r="D182" s="2">
+        <v>0.66747408487888105</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>257</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183" s="2">
+        <v>0.33252195344361501</v>
+      </c>
+      <c r="D183" s="2">
+        <v>0.66747804655638399</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>170</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184" s="2">
+        <v>0.33237817256942198</v>
+      </c>
+      <c r="D184" s="2">
+        <v>0.66762182743057696</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>92</v>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="C185" s="2">
+        <v>0.33216164086719902</v>
+      </c>
+      <c r="D185" s="2">
+        <v>0.66783835913279999</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>232</v>
+      </c>
+      <c r="B186">
+        <v>1</v>
+      </c>
+      <c r="C186" s="2">
+        <v>0.330051377715598</v>
+      </c>
+      <c r="D186" s="2">
+        <v>0.669948622284401</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>249</v>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+      <c r="C187" s="2">
+        <v>0.32990996893159502</v>
+      </c>
+      <c r="D187" s="2">
+        <v>0.67009003106840404</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>12</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188" s="2">
+        <v>0.329647406718653</v>
+      </c>
+      <c r="D188" s="2">
+        <v>0.670352593281346</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>165</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189" s="2">
+        <v>0.32715662493913</v>
+      </c>
+      <c r="D189" s="2">
+        <v>0.672843375060869</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>275</v>
+      </c>
+      <c r="B190">
+        <v>1</v>
+      </c>
+      <c r="C190" s="2">
+        <v>0.32678821604161501</v>
+      </c>
+      <c r="D190" s="2">
+        <v>0.67321178395838399</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>193</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191" s="2">
+        <v>0.326231788050034</v>
+      </c>
+      <c r="D191" s="2">
+        <v>0.67376821194996495</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>93</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+      <c r="C192" s="2">
+        <v>0.32354581702286</v>
+      </c>
+      <c r="D192" s="2">
+        <v>0.676454182977139</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>357</v>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193" s="2">
+        <v>0.32335959722789098</v>
+      </c>
+      <c r="D193" s="2">
+        <v>0.67664040277210802</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>382</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194" s="2">
+        <v>0.31942966400284201</v>
+      </c>
+      <c r="D194" s="2">
+        <v>0.68057033599715799</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>281</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195" s="2">
+        <v>0.317818971653546</v>
+      </c>
+      <c r="D195" s="2">
+        <v>0.682181028346453</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>359</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196" s="2">
+        <v>0.31730943432734798</v>
+      </c>
+      <c r="D196" s="2">
+        <v>0.68269056567265196</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>110</v>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2">
+        <v>0.31699005444084599</v>
+      </c>
+      <c r="D197" s="2">
+        <v>0.68300994555915295</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>42</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198" s="2">
+        <v>0.31602341802245199</v>
+      </c>
+      <c r="D198" s="2">
+        <v>0.68397658197754696</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>190</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199" s="2">
+        <v>0.31571184900468202</v>
+      </c>
+      <c r="D199" s="2">
+        <v>0.68428815099531703</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>200</v>
+      </c>
+      <c r="B200">
+        <v>1</v>
+      </c>
+      <c r="C200" s="2">
+        <v>0.31555514299339299</v>
+      </c>
+      <c r="D200" s="2">
+        <v>0.68444485700660596</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>158</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201" s="2">
+        <v>0.31327244195659598</v>
+      </c>
+      <c r="D201" s="2">
+        <v>0.68672755804340302</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>194</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202" s="2">
+        <v>0.31176723546570501</v>
+      </c>
+      <c r="D202" s="2">
+        <v>0.68823276453429405</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>373</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203" s="2">
+        <v>0.309704324365073</v>
+      </c>
+      <c r="D203" s="2">
+        <v>0.690295675634926</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>55</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204" s="2">
+        <v>0.30902042884405001</v>
+      </c>
+      <c r="D204" s="2">
+        <v>0.69097957115594899</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>166</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205" s="2">
+        <v>0.307490406676588</v>
+      </c>
+      <c r="D205" s="2">
+        <v>0.692509593323411</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>109</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206" s="2">
+        <v>0.30646528367970399</v>
+      </c>
+      <c r="D206" s="2">
+        <v>0.69353471632029495</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>268</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207" s="2">
+        <v>0.30262440210914898</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0.69737559789085002</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>346</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+      <c r="C208" s="2">
+        <v>0.30150861058802098</v>
+      </c>
+      <c r="D208" s="2">
+        <v>0.69849138941197897</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>48</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209" s="2">
+        <v>0.30137524256895099</v>
+      </c>
+      <c r="D209" s="2">
+        <v>0.69862475743104802</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>338</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210" s="2">
+        <v>0.30075960170344601</v>
+      </c>
+      <c r="D210" s="2">
+        <v>0.69924039829655305</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>81</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211" s="2">
+        <v>0.30070557484792598</v>
+      </c>
+      <c r="D211" s="2">
+        <v>0.69929442515207296</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>348</v>
+      </c>
+      <c r="B212">
+        <v>1</v>
+      </c>
+      <c r="C212" s="2">
+        <v>0.30046113046397699</v>
+      </c>
+      <c r="D212" s="2">
+        <v>0.69953886953602196</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>112</v>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213" s="2">
+        <v>0.30014057805655098</v>
+      </c>
+      <c r="D213" s="2">
+        <v>0.69985942194344897</v>
+      </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>144</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214" s="2">
+        <v>0.299860409460599</v>
+      </c>
+      <c r="D214" s="2">
+        <v>0.7001395905394</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>294</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215" s="2">
+        <v>0.29925616136107702</v>
+      </c>
+      <c r="D215" s="2">
+        <v>0.70074383863892198</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>375</v>
+      </c>
+      <c r="B216">
+        <v>1</v>
+      </c>
+      <c r="C216" s="2">
+        <v>0.29769343888509098</v>
+      </c>
+      <c r="D216" s="2">
+        <v>0.70230656111490797</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>176</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217" s="2">
+        <v>0.29756891371646099</v>
+      </c>
+      <c r="D217" s="2">
+        <v>0.70243108628353801</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>73</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218" s="2">
+        <v>0.29630775275148502</v>
+      </c>
+      <c r="D218" s="2">
+        <v>0.70369224724851398</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>229</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219" s="2">
+        <v>0.293774800162516</v>
+      </c>
+      <c r="D219" s="2">
+        <v>0.706225199837483</v>
+      </c>
+      <c r="E219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>271</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220" s="2">
+        <v>0.293192053362474</v>
+      </c>
+      <c r="D220" s="2">
+        <v>0.706807946637525</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>173</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221" s="2">
+        <v>0.29244533845704701</v>
+      </c>
+      <c r="D221" s="2">
+        <v>0.70755466154295199</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>325</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222" s="2">
+        <v>0.292362884790758</v>
+      </c>
+      <c r="D222" s="2">
+        <v>0.707637115209241</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>248</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+      <c r="C223" s="2">
+        <v>0.29076737013153298</v>
+      </c>
+      <c r="D223" s="2">
+        <v>0.70923262986846602</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>395</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224" s="2">
+        <v>0.28951606104317201</v>
+      </c>
+      <c r="D224" s="2">
+        <v>0.71048393895682704</v>
+      </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>207</v>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225" s="2">
+        <v>0.28923921709920603</v>
+      </c>
+      <c r="D225" s="2">
+        <v>0.71076078290079303</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>219</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226" s="2">
+        <v>0.28324976745032598</v>
+      </c>
+      <c r="D226" s="2">
+        <v>0.71675023254967296</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>296</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227" s="2">
+        <v>0.28199995822201401</v>
+      </c>
+      <c r="D227" s="2">
+        <v>0.71800004177798504</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>128</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228" s="2">
+        <v>0.28119678566501699</v>
+      </c>
+      <c r="D228" s="2">
+        <v>0.71880321433498195</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>208</v>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229" s="2">
+        <v>0.28063172859399699</v>
+      </c>
+      <c r="D229" s="2">
+        <v>0.71936827140600201</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>331</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230" s="2">
+        <v>0.27781570733417399</v>
+      </c>
+      <c r="D230" s="2">
+        <v>0.72218429266582496</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>47</v>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231" s="2">
+        <v>0.27710211064376999</v>
+      </c>
+      <c r="D231" s="2">
+        <v>0.72289788935622901</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>147</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232" s="2">
+        <v>0.27554670281010102</v>
+      </c>
+      <c r="D232" s="2">
+        <v>0.72445329718989804</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>295</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233" s="2">
+        <v>0.27374413181205498</v>
+      </c>
+      <c r="D233" s="2">
+        <v>0.72625586818794396</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>293</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234" s="2">
+        <v>0.27318290242094601</v>
+      </c>
+      <c r="D234" s="2">
+        <v>0.726817097579053</v>
+      </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>45</v>
+      </c>
+      <c r="B235">
+        <v>1</v>
+      </c>
+      <c r="C235" s="2">
+        <v>0.27253556424993602</v>
+      </c>
+      <c r="D235" s="2">
+        <v>0.72746443575006303</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>285</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236" s="2">
+        <v>0.27158049470731899</v>
+      </c>
+      <c r="D236" s="2">
+        <v>0.72841950529267996</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>142</v>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237" s="2">
+        <v>0.27063113603419198</v>
+      </c>
+      <c r="D237" s="2">
+        <v>0.72936886396580702</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>298</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238" s="2">
+        <v>0.26898675342452699</v>
+      </c>
+      <c r="D238" s="2">
+        <v>0.73101324657547195</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>137</v>
+      </c>
+      <c r="B239">
+        <v>1</v>
+      </c>
+      <c r="C239" s="2">
+        <v>0.26886434325654102</v>
+      </c>
+      <c r="D239" s="2">
+        <v>0.73113565674345804</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>337</v>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240" s="2">
+        <v>0.26495177030531097</v>
+      </c>
+      <c r="D240" s="2">
+        <v>0.73504822969468797</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>68</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241" s="2">
+        <v>0.26432012208739603</v>
+      </c>
+      <c r="D241" s="2">
+        <v>0.73567987791260303</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>27</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242" s="2">
+        <v>0.26392854987696102</v>
+      </c>
+      <c r="D242" s="2">
+        <v>0.73607145012303798</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>284</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243" s="2">
+        <v>0.26099325252351802</v>
+      </c>
+      <c r="D243" s="2">
+        <v>0.73900674747648099</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>378</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244" s="2">
+        <v>0.25941096366542399</v>
+      </c>
+      <c r="D244" s="2">
+        <v>0.74058903633457496</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>216</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245" s="2">
+        <v>0.258761506146721</v>
+      </c>
+      <c r="D245" s="2">
+        <v>0.741238493853278</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>88</v>
+      </c>
+      <c r="B246">
+        <v>1</v>
+      </c>
+      <c r="C246" s="2">
+        <v>0.25779861717860603</v>
+      </c>
+      <c r="D246" s="2">
+        <v>0.74220138282139303</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>117</v>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247" s="2">
+        <v>0.25728858915584601</v>
+      </c>
+      <c r="D247" s="2">
+        <v>0.74271141084415304</v>
+      </c>
+      <c r="E247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>358</v>
+      </c>
+      <c r="B248">
+        <v>1</v>
+      </c>
+      <c r="C248" s="2">
+        <v>0.25445357710754901</v>
+      </c>
+      <c r="D248" s="2">
+        <v>0.74554642289244999</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>240</v>
+      </c>
+      <c r="B249">
+        <v>1</v>
+      </c>
+      <c r="C249" s="2">
+        <v>0.25358619599469401</v>
+      </c>
+      <c r="D249" s="2">
+        <v>0.74641380400530499</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>99</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250" s="2">
+        <v>0.251155272837155</v>
+      </c>
+      <c r="D250" s="2">
+        <v>0.748844727162844</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>303</v>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251" s="2">
+        <v>0.25084564556503902</v>
+      </c>
+      <c r="D251" s="2">
+        <v>0.74915435443496003</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>244</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252" s="2">
+        <v>0.24920147230790801</v>
+      </c>
+      <c r="D252" s="2">
+        <v>0.75079852769209099</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>335</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253" s="2">
+        <v>0.24738606058746601</v>
+      </c>
+      <c r="D253" s="2">
+        <v>0.75261393941253296</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>228</v>
+      </c>
+      <c r="B254">
+        <v>1</v>
+      </c>
+      <c r="C254" s="2">
+        <v>0.24688002564640901</v>
+      </c>
+      <c r="D254" s="2">
+        <v>0.75311997435359002</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>89</v>
+      </c>
+      <c r="B255">
+        <v>1</v>
+      </c>
+      <c r="C255" s="2">
+        <v>0.245762787463981</v>
+      </c>
+      <c r="D255" s="2">
+        <v>0.75423721253601805</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>230</v>
+      </c>
+      <c r="B256">
+        <v>1</v>
+      </c>
+      <c r="C256" s="2">
+        <v>0.24505919629988099</v>
+      </c>
+      <c r="D256" s="2">
+        <v>0.75494080370011796</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>241</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257" s="2">
+        <v>0.24315245187682499</v>
+      </c>
+      <c r="D257" s="2">
+        <v>0.75684754812317401</v>
+      </c>
+      <c r="E257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>172</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258" s="2">
+        <v>0.242775916142313</v>
+      </c>
+      <c r="D258" s="2">
+        <v>0.75722408385768603</v>
+      </c>
+      <c r="E258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>113</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259" s="2">
+        <v>0.241058229569376</v>
+      </c>
+      <c r="D259" s="2">
+        <v>0.75894177043062305</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>333</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260" s="2">
+        <v>0.24004294574812199</v>
+      </c>
+      <c r="D260" s="2">
+        <v>0.75995705425187798</v>
+      </c>
+      <c r="E260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>183</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261" s="2">
+        <v>0.23777838029922499</v>
+      </c>
+      <c r="D261" s="2">
+        <v>0.76222161970077396</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>310</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262" s="2">
+        <v>0.234067189161943</v>
+      </c>
+      <c r="D262" s="2">
+        <v>0.76593281083805598</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>153</v>
+      </c>
+      <c r="B263">
+        <v>1</v>
+      </c>
+      <c r="C263" s="2">
+        <v>0.23337679864709401</v>
+      </c>
+      <c r="D263" s="2">
+        <v>0.76662320135290596</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>4</v>
+      </c>
+      <c r="B264">
+        <v>1</v>
+      </c>
+      <c r="C264" s="2">
+        <v>0.232119132161165</v>
+      </c>
+      <c r="D264" s="2">
+        <v>0.76788086783883402</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>205</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265" s="2">
+        <v>0.231983282287378</v>
+      </c>
+      <c r="D265" s="2">
+        <v>0.76801671771262103</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>218</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266" s="2">
+        <v>0.229074471093861</v>
+      </c>
+      <c r="D266" s="2">
+        <v>0.77092552890613897</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>302</v>
+      </c>
+      <c r="B267">
+        <v>1</v>
+      </c>
+      <c r="C267" s="2">
+        <v>0.228282541273229</v>
+      </c>
+      <c r="D267" s="2">
+        <v>0.77171745872677</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>301</v>
+      </c>
+      <c r="B268">
+        <v>1</v>
+      </c>
+      <c r="C268" s="2">
+        <v>0.228181169590225</v>
+      </c>
+      <c r="D268" s="2">
+        <v>0.77181883040977395</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>292</v>
+      </c>
+      <c r="B269">
+        <v>1</v>
+      </c>
+      <c r="C269" s="2">
+        <v>0.226095186262498</v>
+      </c>
+      <c r="D269" s="2">
+        <v>0.77390481373750097</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>270</v>
+      </c>
+      <c r="B270">
+        <v>1</v>
+      </c>
+      <c r="C270" s="2">
+        <v>0.222126658861098</v>
+      </c>
+      <c r="D270" s="2">
+        <v>0.77787334113890105</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>380</v>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+      <c r="C271" s="2">
+        <v>0.221651020308201</v>
+      </c>
+      <c r="D271" s="2">
+        <v>0.77834897969179895</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>278</v>
+      </c>
+      <c r="B272">
+        <v>1</v>
+      </c>
+      <c r="C272" s="2">
+        <v>0.221082797625095</v>
+      </c>
+      <c r="D272" s="2">
+        <v>0.77891720237490403</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>107</v>
+      </c>
+      <c r="B273">
+        <v>1</v>
+      </c>
+      <c r="C273" s="2">
+        <v>0.21920465098860301</v>
+      </c>
+      <c r="D273" s="2">
+        <v>0.78079534901139602</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>167</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274" s="2">
+        <v>0.21891851682114299</v>
+      </c>
+      <c r="D274" s="2">
+        <v>0.78108148317885595</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>17</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275" s="2">
+        <v>0.218847660579087</v>
+      </c>
+      <c r="D275" s="2">
+        <v>0.781152339420912</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>314</v>
+      </c>
+      <c r="B276">
+        <v>1</v>
+      </c>
+      <c r="C276" s="2">
+        <v>0.21638057887512099</v>
+      </c>
+      <c r="D276" s="2">
+        <v>0.78361942112487804</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>95</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277" s="2">
+        <v>0.21634993691925999</v>
+      </c>
+      <c r="D277" s="2">
+        <v>0.78365006308073903</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>362</v>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278" s="2">
+        <v>0.21564774482812299</v>
+      </c>
+      <c r="D278" s="2">
+        <v>0.78435225517187601</v>
+      </c>
+      <c r="E278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>349</v>
+      </c>
+      <c r="B279">
+        <v>1</v>
+      </c>
+      <c r="C279" s="2">
+        <v>0.21418280292561201</v>
+      </c>
+      <c r="D279" s="2">
+        <v>0.78581719707438702</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>391</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280" s="2">
+        <v>0.213201578455189</v>
+      </c>
+      <c r="D280" s="2">
+        <v>0.78679842154480994</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>80</v>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
+      <c r="C281" s="2">
+        <v>0.21123644945783099</v>
+      </c>
+      <c r="D281" s="2">
+        <v>0.78876355054216796</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>250</v>
+      </c>
+      <c r="B282">
+        <v>1</v>
+      </c>
+      <c r="C282" s="2">
+        <v>0.209999852324256</v>
+      </c>
+      <c r="D282" s="2">
+        <v>0.790000147675743</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>70</v>
+      </c>
+      <c r="B283">
+        <v>1</v>
+      </c>
+      <c r="C283" s="2">
+        <v>0.20754281370403799</v>
+      </c>
+      <c r="D283" s="2">
+        <v>0.79245718629596096</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284" s="2">
+        <v>0.20026538233142899</v>
+      </c>
+      <c r="D284" s="2">
+        <v>0.79973461766857001</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>321</v>
+      </c>
+      <c r="B285">
+        <v>1</v>
+      </c>
+      <c r="C285" s="2">
+        <v>0.20004736023532599</v>
+      </c>
+      <c r="D285" s="2">
+        <v>0.79995263976467301</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>101</v>
+      </c>
+      <c r="B286">
+        <v>1</v>
+      </c>
+      <c r="C286" s="2">
+        <v>0.19860742269130699</v>
+      </c>
+      <c r="D286" s="2">
+        <v>0.80139257730869196</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>72</v>
+      </c>
+      <c r="B287">
+        <v>1</v>
+      </c>
+      <c r="C287" s="2">
+        <v>0.196580855402927</v>
+      </c>
+      <c r="D287" s="2">
+        <v>0.80341914459707198</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>393</v>
+      </c>
+      <c r="B288">
+        <v>1</v>
+      </c>
+      <c r="C288" s="2">
+        <v>0.196165976432077</v>
+      </c>
+      <c r="D288" s="2">
+        <v>0.803834023567922</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>324</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289" s="2">
+        <v>0.192981801475509</v>
+      </c>
+      <c r="D289" s="2">
+        <v>0.80701819852448997</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>123</v>
+      </c>
+      <c r="B290">
+        <v>1</v>
+      </c>
+      <c r="C290" s="2">
+        <v>0.19250822863575001</v>
+      </c>
+      <c r="D290" s="2">
+        <v>0.80749177136424899</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>35</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291" s="2">
+        <v>0.18906972146261999</v>
+      </c>
+      <c r="D291" s="2">
+        <v>0.81093027853737898</v>
+      </c>
+      <c r="E291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>308</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292" s="2">
+        <v>0.187990830009645</v>
+      </c>
+      <c r="D292" s="2">
+        <v>0.812009169990354</v>
+      </c>
+      <c r="E292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>50</v>
+      </c>
+      <c r="B293">
+        <v>1</v>
+      </c>
+      <c r="C293" s="2">
+        <v>0.186834984626019</v>
+      </c>
+      <c r="D293" s="2">
+        <v>0.813165015373981</v>
+      </c>
+      <c r="E293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>398</v>
+      </c>
+      <c r="B294">
+        <v>1</v>
+      </c>
+      <c r="C294" s="2">
+        <v>0.18539601473359399</v>
+      </c>
+      <c r="D294" s="2">
+        <v>0.81460398526640498</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>369</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+      <c r="C295" s="2">
+        <v>0.18485029987608001</v>
+      </c>
+      <c r="D295" s="2">
+        <v>0.81514970012391896</v>
+      </c>
+      <c r="E295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>238</v>
+      </c>
+      <c r="B296">
+        <v>1</v>
+      </c>
+      <c r="C296" s="2">
+        <v>0.18479289542483801</v>
+      </c>
+      <c r="D296" s="2">
+        <v>0.81520710457516199</v>
+      </c>
+      <c r="E296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>116</v>
+      </c>
+      <c r="B297">
+        <v>1</v>
+      </c>
+      <c r="C297" s="2">
+        <v>0.182977159439841</v>
+      </c>
+      <c r="D297" s="2">
+        <v>0.81702284056015795</v>
+      </c>
+      <c r="E297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>71</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298" s="2">
+        <v>0.17775590926644699</v>
+      </c>
+      <c r="D298" s="2">
+        <v>0.82224409073355298</v>
+      </c>
+      <c r="E298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>306</v>
+      </c>
+      <c r="B299">
+        <v>1</v>
+      </c>
+      <c r="C299" s="2">
+        <v>0.17751077104589399</v>
+      </c>
+      <c r="D299" s="2">
+        <v>0.82248922895410503</v>
+      </c>
+      <c r="E299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>262</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300" s="2">
+        <v>0.17624644158295</v>
+      </c>
+      <c r="D300" s="2">
+        <v>0.823753558417049</v>
+      </c>
+      <c r="E300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>187</v>
+      </c>
+      <c r="B301">
+        <v>1</v>
+      </c>
+      <c r="C301" s="2">
+        <v>0.17563520788711501</v>
+      </c>
+      <c r="D301" s="2">
+        <v>0.82436479211288405</v>
+      </c>
+      <c r="E301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>351</v>
+      </c>
+      <c r="B302">
+        <v>1</v>
+      </c>
+      <c r="C302" s="2">
+        <v>0.17484992424090801</v>
+      </c>
+      <c r="D302" s="2">
+        <v>0.82515007575909105</v>
+      </c>
+      <c r="E302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>59</v>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+      <c r="C303" s="2">
+        <v>0.17295166446565099</v>
+      </c>
+      <c r="D303" s="2">
+        <v>0.82704833553434798</v>
+      </c>
+      <c r="E303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>213</v>
+      </c>
+      <c r="B304">
+        <v>1</v>
+      </c>
+      <c r="C304" s="2">
+        <v>0.172493215668758</v>
+      </c>
+      <c r="D304" s="2">
+        <v>0.82750678433124103</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>87</v>
+      </c>
+      <c r="B305">
+        <v>1</v>
+      </c>
+      <c r="C305" s="2">
+        <v>0.172363063204619</v>
+      </c>
+      <c r="D305" s="2">
+        <v>0.82763693679538097</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>14</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306" s="2">
+        <v>0.17013659553534799</v>
+      </c>
+      <c r="D306" s="2">
+        <v>0.82986340446465101</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>132</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307" s="2">
+        <v>0.16978387567657399</v>
+      </c>
+      <c r="D307" s="2">
+        <v>0.83021612432342495</v>
+      </c>
+      <c r="E307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>332</v>
+      </c>
+      <c r="B308">
+        <v>1</v>
+      </c>
+      <c r="C308" s="2">
+        <v>0.16894138655559199</v>
+      </c>
+      <c r="D308" s="2">
+        <v>0.83105861344440801</v>
+      </c>
+      <c r="E308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>25</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309" s="2">
+        <v>0.16869384867392501</v>
+      </c>
+      <c r="D309" s="2">
+        <v>0.83130615132607399</v>
+      </c>
+      <c r="E309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>287</v>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310" s="2">
+        <v>0.16712433999908299</v>
+      </c>
+      <c r="D310" s="2">
+        <v>0.83287566000091595</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>84</v>
+      </c>
+      <c r="B311">
+        <v>1</v>
+      </c>
+      <c r="C311" s="2">
+        <v>0.16698835353001401</v>
+      </c>
+      <c r="D311" s="2">
+        <v>0.83301164646998505</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>345</v>
+      </c>
+      <c r="B312">
+        <v>1</v>
+      </c>
+      <c r="C312" s="2">
+        <v>0.16639470142360299</v>
+      </c>
+      <c r="D312" s="2">
+        <v>0.83360529857639598</v>
+      </c>
+      <c r="E312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>255</v>
+      </c>
+      <c r="B313">
+        <v>1</v>
+      </c>
+      <c r="C313" s="2">
+        <v>0.164910788500475</v>
+      </c>
+      <c r="D313" s="2">
+        <v>0.83508921149952398</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>126</v>
+      </c>
+      <c r="B314">
+        <v>1</v>
+      </c>
+      <c r="C314" s="2">
+        <v>0.164858029819788</v>
+      </c>
+      <c r="D314" s="2">
+        <v>0.83514197018021097</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>353</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315" s="2">
+        <v>0.162758664718509</v>
+      </c>
+      <c r="D315" s="2">
+        <v>0.83724133528149003</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>192</v>
+      </c>
+      <c r="B316">
+        <v>1</v>
+      </c>
+      <c r="C316" s="2">
+        <v>0.16257984272083301</v>
+      </c>
+      <c r="D316" s="2">
+        <v>0.83742015727916597</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>61</v>
+      </c>
+      <c r="B317">
+        <v>1</v>
+      </c>
+      <c r="C317" s="2">
+        <v>0.16126414372843301</v>
+      </c>
+      <c r="D317" s="2">
+        <v>0.83873585627156699</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>266</v>
+      </c>
+      <c r="B318">
+        <v>1</v>
+      </c>
+      <c r="C318" s="2">
+        <v>0.158637346655433</v>
+      </c>
+      <c r="D318" s="2">
+        <v>0.84136265334456595</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>148</v>
+      </c>
+      <c r="B319">
+        <v>1</v>
+      </c>
+      <c r="C319" s="2">
+        <v>0.15664168779430901</v>
+      </c>
+      <c r="D319" s="2">
+        <v>0.84335831220569002</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>197</v>
+      </c>
+      <c r="B320">
+        <v>1</v>
+      </c>
+      <c r="C320" s="2">
+        <v>0.155593233054059</v>
+      </c>
+      <c r="D320" s="2">
+        <v>0.84440676694593997</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>212</v>
+      </c>
+      <c r="B321">
+        <v>1</v>
+      </c>
+      <c r="C321" s="2">
+        <v>0.15468352469237001</v>
+      </c>
+      <c r="D321" s="2">
+        <v>0.84531647530762899</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>100</v>
+      </c>
+      <c r="B322">
+        <v>1</v>
+      </c>
+      <c r="C322" s="2">
+        <v>0.153928066967398</v>
+      </c>
+      <c r="D322" s="2">
+        <v>0.84607193303260098</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>317</v>
+      </c>
+      <c r="B323">
+        <v>1</v>
+      </c>
+      <c r="C323" s="2">
+        <v>0.15182142614027</v>
+      </c>
+      <c r="D323" s="2">
+        <v>0.84817857385972895</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>201</v>
+      </c>
+      <c r="B324">
+        <v>1</v>
+      </c>
+      <c r="C324" s="2">
+        <v>0.149106990034095</v>
+      </c>
+      <c r="D324" s="2">
+        <v>0.850893009965904</v>
+      </c>
+      <c r="E324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>290</v>
+      </c>
+      <c r="B325">
+        <v>1</v>
+      </c>
+      <c r="C325" s="2">
+        <v>0.148766680498265</v>
+      </c>
+      <c r="D325" s="2">
+        <v>0.85123331950173398</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>254</v>
+      </c>
+      <c r="B326">
+        <v>1</v>
+      </c>
+      <c r="C326" s="2">
+        <v>0.14627891227098699</v>
+      </c>
+      <c r="D326" s="2">
+        <v>0.85372108772901201</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>203</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327" s="2">
+        <v>0.14578443815223799</v>
+      </c>
+      <c r="D327" s="2">
+        <v>0.85421556184776104</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>9</v>
+      </c>
+      <c r="B328">
+        <v>1</v>
+      </c>
+      <c r="C328" s="2">
+        <v>0.144444899221119</v>
+      </c>
+      <c r="D328" s="2">
+        <v>0.85555510077887997</v>
+      </c>
+      <c r="E328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>66</v>
+      </c>
+      <c r="B329">
+        <v>1</v>
+      </c>
+      <c r="C329" s="2">
+        <v>0.14435823152301699</v>
+      </c>
+      <c r="D329" s="2">
+        <v>0.85564176847698203</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>182</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330" s="2">
+        <v>0.14433862793601299</v>
+      </c>
+      <c r="D330" s="2">
+        <v>0.85566137206398596</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>364</v>
+      </c>
+      <c r="B331">
+        <v>1</v>
+      </c>
+      <c r="C331" s="2">
+        <v>0.14317247958892301</v>
+      </c>
+      <c r="D331" s="2">
+        <v>0.85682752041107602</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>274</v>
+      </c>
+      <c r="B332">
+        <v>1</v>
+      </c>
+      <c r="C332" s="2">
+        <v>0.14086257286939299</v>
+      </c>
+      <c r="D332" s="2">
+        <v>0.85913742713060604</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>130</v>
+      </c>
+      <c r="B333">
+        <v>1</v>
+      </c>
+      <c r="C333" s="2">
+        <v>0.13865003659863501</v>
+      </c>
+      <c r="D333" s="2">
+        <v>0.86134996340136405</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>85</v>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334" s="2">
+        <v>0.13830757054399101</v>
+      </c>
+      <c r="D334" s="2">
+        <v>0.86169242945600799</v>
+      </c>
+      <c r="E334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>394</v>
+      </c>
+      <c r="B335">
+        <v>1</v>
+      </c>
+      <c r="C335" s="2">
+        <v>0.135367077456225</v>
+      </c>
+      <c r="D335" s="2">
+        <v>0.864632922543774</v>
+      </c>
+      <c r="E335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>226</v>
+      </c>
+      <c r="B336">
+        <v>1</v>
+      </c>
+      <c r="C336" s="2">
+        <v>0.13509044679975901</v>
+      </c>
+      <c r="D336" s="2">
+        <v>0.86490955320023999</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>11</v>
+      </c>
+      <c r="B337">
+        <v>1</v>
+      </c>
+      <c r="C337" s="2">
+        <v>0.13460563458031799</v>
+      </c>
+      <c r="D337" s="2">
+        <v>0.86539436541968096</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>388</v>
+      </c>
+      <c r="B338">
+        <v>1</v>
+      </c>
+      <c r="C338" s="2">
+        <v>0.134462758336855</v>
+      </c>
+      <c r="D338" s="2">
+        <v>0.86553724166314405</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>134</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339" s="2">
+        <v>0.13401507233370399</v>
+      </c>
+      <c r="D339" s="2">
+        <v>0.86598492766629498</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>8</v>
+      </c>
+      <c r="B340">
+        <v>1</v>
+      </c>
+      <c r="C340" s="2">
+        <v>0.132515134311087</v>
+      </c>
+      <c r="D340" s="2">
+        <v>0.86748486568891203</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>75</v>
+      </c>
+      <c r="B341">
+        <v>1</v>
+      </c>
+      <c r="C341" s="2">
+        <v>0.13108982553902301</v>
+      </c>
+      <c r="D341" s="2">
+        <v>0.86891017446097596</v>
+      </c>
+      <c r="E341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>260</v>
+      </c>
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342" s="2">
+        <v>0.130388099956985</v>
+      </c>
+      <c r="D342" s="2">
+        <v>0.86961190004301403</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>23</v>
+      </c>
+      <c r="B343">
+        <v>1</v>
+      </c>
+      <c r="C343" s="2">
+        <v>0.12814770184327301</v>
+      </c>
+      <c r="D343" s="2">
+        <v>0.87185229815672605</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>367</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344" s="2">
+        <v>0.12787577977477699</v>
+      </c>
+      <c r="D344" s="2">
+        <v>0.87212422022522196</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>104</v>
+      </c>
+      <c r="B345">
+        <v>1</v>
+      </c>
+      <c r="C345" s="2">
+        <v>0.12522590979151499</v>
+      </c>
+      <c r="D345" s="2">
+        <v>0.87477409020848496</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>13</v>
+      </c>
+      <c r="B346">
+        <v>1</v>
+      </c>
+      <c r="C346" s="2">
+        <v>0.124641159433229</v>
+      </c>
+      <c r="D346" s="2">
+        <v>0.87535884056677005</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>311</v>
+      </c>
+      <c r="B347">
+        <v>1</v>
+      </c>
+      <c r="C347" s="2">
+        <v>0.123798192581082</v>
+      </c>
+      <c r="D347" s="2">
+        <v>0.87620180741891696</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>304</v>
+      </c>
+      <c r="B348">
+        <v>1</v>
+      </c>
+      <c r="C348" s="2">
+        <v>0.122263799627587</v>
+      </c>
+      <c r="D348" s="2">
+        <v>0.87773620037241196</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>185</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349" s="2">
+        <v>0.121533068769257</v>
+      </c>
+      <c r="D349" s="2">
+        <v>0.87846693123074204</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>225</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350" s="2">
+        <v>0.11888060067003201</v>
+      </c>
+      <c r="D350" s="2">
+        <v>0.88111939932996697</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>223</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351" s="2">
+        <v>0.118420113216181</v>
+      </c>
+      <c r="D351" s="2">
+        <v>0.88157988678381805</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>124</v>
+      </c>
+      <c r="B352">
+        <v>1</v>
+      </c>
+      <c r="C352" s="2">
+        <v>0.117609338436776</v>
+      </c>
+      <c r="D352" s="2">
+        <v>0.88239066156322299</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>140</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353" s="2">
+        <v>0.117280992114618</v>
+      </c>
+      <c r="D353" s="2">
+        <v>0.88271900788538105</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>160</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354" s="2">
+        <v>0.116923082189252</v>
+      </c>
+      <c r="D354" s="2">
+        <v>0.88307691781074704</v>
+      </c>
+      <c r="E354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>204</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355" s="2">
+        <v>0.11670704173786001</v>
+      </c>
+      <c r="D355" s="2">
+        <v>0.88329295826213905</v>
+      </c>
+      <c r="E355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>54</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356" s="2">
+        <v>0.115073327708979</v>
+      </c>
+      <c r="D356" s="2">
+        <v>0.88492667229101996</v>
+      </c>
+      <c r="E356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>221</v>
+      </c>
+      <c r="B357">
+        <v>1</v>
+      </c>
+      <c r="C357" s="2">
+        <v>0.114818543076169</v>
+      </c>
+      <c r="D357" s="2">
+        <v>0.88518145692382999</v>
+      </c>
+      <c r="E357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>168</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358" s="2">
+        <v>0.11474333455334999</v>
+      </c>
+      <c r="D358" s="2">
+        <v>0.88525666544664905</v>
+      </c>
+      <c r="E358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>396</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359" s="2">
+        <v>0.113932462611348</v>
+      </c>
+      <c r="D359" s="2">
+        <v>0.88606753738865096</v>
+      </c>
+      <c r="E359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>76</v>
+      </c>
+      <c r="B360">
+        <v>1</v>
+      </c>
+      <c r="C360" s="2">
+        <v>0.11366976429652299</v>
+      </c>
+      <c r="D360" s="2">
+        <v>0.88633023570347602</v>
+      </c>
+      <c r="E360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>191</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361" s="2">
+        <v>0.11363577711256199</v>
+      </c>
+      <c r="D361" s="2">
+        <v>0.88636422288743699</v>
+      </c>
+      <c r="E361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>37</v>
+      </c>
+      <c r="B362">
+        <v>1</v>
+      </c>
+      <c r="C362" s="2">
+        <v>0.112465090885733</v>
+      </c>
+      <c r="D362" s="2">
+        <v>0.88753490911426602</v>
+      </c>
+      <c r="E362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>33</v>
+      </c>
+      <c r="B363">
+        <v>1</v>
+      </c>
+      <c r="C363" s="2">
+        <v>0.11154210066959699</v>
+      </c>
+      <c r="D363" s="2">
+        <v>0.88845789933040198</v>
+      </c>
+      <c r="E363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>215</v>
+      </c>
+      <c r="B364">
+        <v>1</v>
+      </c>
+      <c r="C364" s="2">
+        <v>0.11004715587545599</v>
+      </c>
+      <c r="D364" s="2">
+        <v>0.88995284412454301</v>
+      </c>
+      <c r="E364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>118</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365" s="2">
+        <v>0.11000390642123201</v>
+      </c>
+      <c r="D365" s="2">
+        <v>0.88999609357876697</v>
+      </c>
+      <c r="E365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>38</v>
+      </c>
+      <c r="B366">
+        <v>1</v>
+      </c>
+      <c r="C366" s="2">
+        <v>0.108488790967656</v>
+      </c>
+      <c r="D366" s="2">
+        <v>0.89151120903234304</v>
+      </c>
+      <c r="E366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>392</v>
+      </c>
+      <c r="B367">
+        <v>1</v>
+      </c>
+      <c r="C367" s="2">
+        <v>0.108165510067983</v>
+      </c>
+      <c r="D367" s="2">
+        <v>0.89183448993201597</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>34</v>
+      </c>
+      <c r="B368">
+        <v>1</v>
+      </c>
+      <c r="C368" s="2">
+        <v>0.107358052943587</v>
+      </c>
+      <c r="D368" s="2">
+        <v>0.89264194705641298</v>
+      </c>
+      <c r="E368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>125</v>
+      </c>
+      <c r="B369">
+        <v>1</v>
+      </c>
+      <c r="C369" s="2">
+        <v>0.107324056404802</v>
+      </c>
+      <c r="D369" s="2">
+        <v>0.89267594359519697</v>
+      </c>
+      <c r="E369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>235</v>
+      </c>
+      <c r="B370">
+        <v>1</v>
+      </c>
+      <c r="C370" s="2">
+        <v>0.102903754003495</v>
+      </c>
+      <c r="D370" s="2">
+        <v>0.89709624599650395</v>
+      </c>
+      <c r="E370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>340</v>
+      </c>
+      <c r="B371">
+        <v>1</v>
+      </c>
+      <c r="C371" s="2">
+        <v>0.101896343794128</v>
+      </c>
+      <c r="D371" s="2">
+        <v>0.89810365620587096</v>
+      </c>
+      <c r="E371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>305</v>
+      </c>
+      <c r="B372">
+        <v>1</v>
+      </c>
+      <c r="C372" s="2">
+        <v>0.100761668496054</v>
+      </c>
+      <c r="D372" s="2">
+        <v>0.89923833150394505</v>
+      </c>
+      <c r="E372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>115</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373" s="2">
+        <v>0.100125151845101</v>
+      </c>
+      <c r="D373" s="2">
+        <v>0.89987484815489804</v>
+      </c>
+      <c r="E373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>83</v>
+      </c>
+      <c r="B374">
+        <v>1</v>
+      </c>
+      <c r="C374" s="2">
+        <v>9.9194297389389702E-2</v>
+      </c>
+      <c r="D374" s="2">
+        <v>0.90080570261060999</v>
+      </c>
+      <c r="E374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>39</v>
+      </c>
+      <c r="B375">
+        <v>1</v>
+      </c>
+      <c r="C375" s="2">
+        <v>9.9027356285356596E-2</v>
+      </c>
+      <c r="D375" s="2">
+        <v>0.90097264371464303</v>
+      </c>
+      <c r="E375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>152</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376" s="2">
+        <v>9.6431120277745905E-2</v>
+      </c>
+      <c r="D376" s="2">
+        <v>0.90356887972225397</v>
+      </c>
+      <c r="E376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>372</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377" s="2">
+        <v>9.4369067031179907E-2</v>
+      </c>
+      <c r="D377" s="2">
+        <v>0.90563093296882002</v>
+      </c>
+      <c r="E377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>247</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378" s="2">
+        <v>9.3970191702778594E-2</v>
+      </c>
+      <c r="D378" s="2">
+        <v>0.90602980829722102</v>
+      </c>
+      <c r="E378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>222</v>
+      </c>
+      <c r="B379">
+        <v>1</v>
+      </c>
+      <c r="C379" s="2">
+        <v>9.3575518763545598E-2</v>
+      </c>
+      <c r="D379" s="2">
+        <v>0.90642448123645403</v>
+      </c>
+      <c r="E379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>30</v>
+      </c>
+      <c r="B380">
+        <v>1</v>
+      </c>
+      <c r="C380" s="2">
+        <v>9.2925509080634794E-2</v>
+      </c>
+      <c r="D380" s="2">
+        <v>0.90707449091936498</v>
+      </c>
+      <c r="E380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>224</v>
+      </c>
+      <c r="B381">
+        <v>1</v>
+      </c>
+      <c r="C381" s="2">
+        <v>9.0384901900281395E-2</v>
+      </c>
+      <c r="D381" s="2">
+        <v>0.90961509809971797</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>242</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382" s="2">
+        <v>8.7827184360941904E-2</v>
+      </c>
+      <c r="D382" s="2">
+        <v>0.91217281563905805</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>336</v>
+      </c>
+      <c r="B383">
+        <v>1</v>
+      </c>
+      <c r="C383" s="2">
+        <v>8.6372432368955601E-2</v>
+      </c>
+      <c r="D383" s="2">
+        <v>0.91362756763104402</v>
+      </c>
+      <c r="E383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>58</v>
+      </c>
+      <c r="B384">
+        <v>1</v>
+      </c>
+      <c r="C384" s="2">
+        <v>8.5862274993122004E-2</v>
+      </c>
+      <c r="D384" s="2">
+        <v>0.91413772500687795</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>150</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385" s="2">
+        <v>8.4669761835666199E-2</v>
+      </c>
+      <c r="D385" s="2">
+        <v>0.91533023816433301</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>135</v>
+      </c>
+      <c r="B386">
+        <v>1</v>
+      </c>
+      <c r="C386" s="2">
+        <v>8.4544949832619398E-2</v>
+      </c>
+      <c r="D386" s="2">
+        <v>0.91545505016738005</v>
+      </c>
+      <c r="E386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>379</v>
+      </c>
+      <c r="B387">
+        <v>1</v>
+      </c>
+      <c r="C387" s="2">
+        <v>8.4025489097265205E-2</v>
+      </c>
+      <c r="D387" s="2">
+        <v>0.91597451090273396</v>
+      </c>
+      <c r="E387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>371</v>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388" s="2">
+        <v>8.1077552855233104E-2</v>
+      </c>
+      <c r="D388" s="2">
+        <v>0.91892244714476601</v>
+      </c>
+      <c r="E388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>354</v>
+      </c>
+      <c r="B389">
+        <v>1</v>
+      </c>
+      <c r="C389" s="2">
+        <v>7.6682959601266004E-2</v>
+      </c>
+      <c r="D389" s="2">
+        <v>0.92331704039873397</v>
+      </c>
+      <c r="E389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>276</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390" s="2">
+        <v>7.3868210807919998E-2</v>
+      </c>
+      <c r="D390" s="2">
+        <v>0.92613178919207995</v>
+      </c>
+      <c r="E390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>352</v>
+      </c>
+      <c r="B391">
+        <v>1</v>
+      </c>
+      <c r="C391" s="2">
+        <v>6.8460558867534105E-2</v>
+      </c>
+      <c r="D391" s="2">
+        <v>0.93153944113246501</v>
+      </c>
+      <c r="E391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>91</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392" s="2">
+        <v>6.7753473930911898E-2</v>
+      </c>
+      <c r="D392" s="2">
+        <v>0.93224652606908798</v>
+      </c>
+      <c r="E392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>5</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393" s="2">
+        <v>6.6907890345421397E-2</v>
+      </c>
+      <c r="D393" s="2">
+        <v>0.93309210965457801</v>
+      </c>
+      <c r="E393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>309</v>
+      </c>
+      <c r="B394">
+        <v>1</v>
+      </c>
+      <c r="C394" s="2">
+        <v>6.5327856328408596E-2</v>
+      </c>
+      <c r="D394" s="2">
+        <v>0.93467214367159102</v>
+      </c>
+      <c r="E394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>145</v>
+      </c>
+      <c r="B395">
+        <v>1</v>
+      </c>
+      <c r="C395" s="2">
+        <v>6.5322544728043996E-2</v>
+      </c>
+      <c r="D395" s="2">
+        <v>0.934677455271956</v>
+      </c>
+      <c r="E395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>114</v>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396" s="2">
+        <v>6.4694371178253898E-2</v>
+      </c>
+      <c r="D396" s="2">
+        <v>0.93530562882174595</v>
+      </c>
+      <c r="E396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>286</v>
+      </c>
+      <c r="B397">
+        <v>1</v>
+      </c>
+      <c r="C397" s="2">
+        <v>6.0548217203128397E-2</v>
+      </c>
+      <c r="D397" s="2">
+        <v>0.93945178279687103</v>
+      </c>
+      <c r="E397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>245</v>
+      </c>
+      <c r="B398">
+        <v>1</v>
+      </c>
+      <c r="C398" s="2">
+        <v>5.7445627964969201E-2</v>
+      </c>
+      <c r="D398" s="2">
+        <v>0.94255437203503001</v>
+      </c>
+      <c r="E398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>44</v>
+      </c>
+      <c r="B399">
+        <v>1</v>
+      </c>
+      <c r="C399" s="2">
+        <v>5.5949471568144303E-2</v>
+      </c>
+      <c r="D399" s="2">
+        <v>0.944050528431855</v>
+      </c>
+      <c r="E399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>189</v>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400" s="2">
+        <v>4.6918077701862099E-2</v>
+      </c>
+      <c r="D400" s="2">
+        <v>0.95308192229813704</v>
+      </c>
+      <c r="E400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>377</v>
+      </c>
+      <c r="B401">
+        <v>1</v>
+      </c>
+      <c r="C401" s="2">
+        <v>4.6779713268150502E-2</v>
+      </c>
+      <c r="D401" s="2">
+        <v>0.953220286731849</v>
+      </c>
+      <c r="E401">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/result_analysis/analysis.xlsx
+++ b/result_analysis/analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tintin/Desktop/Projects/credit_risk_model/result_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB81ED7-E03B-4143-B776-B8A16D9A4D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AD8A9-8B83-494F-923B-9DE01BD2FBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{61FC1A9A-6CB0-D841-9DA7-4D6ECF9C438C}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">raw_data!$A$1:$E$1</definedName>
     <definedName name="results" localSheetId="0">raw_data!$B$1:$E$401</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{19AAA4B1-3FBF-7941-859B-50199E752304}" name="results" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/tintin/Desktop/Projects/credit_risk_model/model/results.csv" comma="1">
+    <textPr sourceFile="/Users/tintin/Desktop/Projects/credit_risk_model/model/results.csv" comma="1">
       <textFields count="4">
         <textField/>
         <textField/>
@@ -176,7 +176,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}" name="Table1" displayName="Table1" ref="A1:E401" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:E401" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E401">
-    <sortCondition descending="1" ref="C1:C1048576"/>
+    <sortCondition descending="1" ref="D1:D401"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A33D2E8F-C4FE-744C-B6EA-6D08D082939C}" name="index"/>
@@ -7746,1563 +7746,1563 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>0.82503400713532005</v>
+        <v>4.6779713268150502E-2</v>
       </c>
       <c r="D2" s="2">
-        <v>0.17496599286467901</v>
+        <v>0.953220286731849</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>330</v>
+        <v>189</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>0.82158174384212701</v>
+        <v>4.6918077701862099E-2</v>
       </c>
       <c r="D3" s="2">
-        <v>0.17841825615787199</v>
+        <v>0.95308192229813704</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>341</v>
+        <v>44</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>0.80794744749740299</v>
+        <v>5.5949471568144303E-2</v>
       </c>
       <c r="D4" s="2">
-        <v>0.19205255250259601</v>
+        <v>0.944050528431855</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>0.77347535673464496</v>
+        <v>5.7445627964969201E-2</v>
       </c>
       <c r="D5" s="2">
-        <v>0.22652464326535399</v>
+        <v>0.94255437203503001</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>52</v>
+        <v>286</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>0.76692651002603096</v>
+        <v>6.0548217203128397E-2</v>
       </c>
       <c r="D6" s="2">
-        <v>0.23307348997396801</v>
+        <v>0.93945178279687103</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>0.76663505665523601</v>
+        <v>6.4694371178253898E-2</v>
       </c>
       <c r="D7" s="2">
-        <v>0.23336494334476299</v>
+        <v>0.93530562882174595</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>0.765516263403206</v>
+        <v>6.5322544728043996E-2</v>
       </c>
       <c r="D8" s="2">
-        <v>0.234483736596793</v>
+        <v>0.934677455271956</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>105</v>
+        <v>309</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2">
-        <v>0.76031332844253696</v>
+        <v>6.5327856328408596E-2</v>
       </c>
       <c r="D9" s="2">
-        <v>0.23968667155746201</v>
+        <v>0.93467214367159102</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>0.76025575181913996</v>
+        <v>6.6907890345421397E-2</v>
       </c>
       <c r="D10" s="2">
-        <v>0.23974424818085899</v>
+        <v>0.93309210965457801</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0.75702518889234005</v>
+        <v>6.7753473930911898E-2</v>
       </c>
       <c r="D11" s="2">
-        <v>0.24297481110765901</v>
+        <v>0.93224652606908798</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>234</v>
+        <v>352</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>0.75672824354326695</v>
+        <v>6.8460558867534105E-2</v>
       </c>
       <c r="D12" s="2">
-        <v>0.24327175645673199</v>
+        <v>0.93153944113246501</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>181</v>
+        <v>276</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>0.75312170932141098</v>
+        <v>7.3868210807919998E-2</v>
       </c>
       <c r="D13" s="2">
-        <v>0.24687829067858799</v>
+        <v>0.92613178919207995</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>0.74606387404385499</v>
+        <v>7.6682959601266004E-2</v>
       </c>
       <c r="D14" s="2">
-        <v>0.25393612595614401</v>
+        <v>0.92331704039873397</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>0.74440235035125202</v>
+        <v>8.1077552855233104E-2</v>
       </c>
       <c r="D15" s="2">
-        <v>0.25559764964874698</v>
+        <v>0.91892244714476601</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>264</v>
+        <v>379</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
-        <v>0.72339284582967001</v>
+        <v>8.4025489097265205E-2</v>
       </c>
       <c r="D16" s="2">
-        <v>0.27660715417032899</v>
+        <v>0.91597451090273396</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>368</v>
+        <v>135</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2">
-        <v>0.72274873403993301</v>
+        <v>8.4544949832619398E-2</v>
       </c>
       <c r="D17" s="2">
-        <v>0.277251265960066</v>
+        <v>0.91545505016738005</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0.720072153616232</v>
+        <v>8.4669761835666199E-2</v>
       </c>
       <c r="D18" s="2">
-        <v>0.279927846383767</v>
+        <v>0.91533023816433301</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="2">
-        <v>0.71976402939073203</v>
+        <v>8.5862274993122004E-2</v>
       </c>
       <c r="D19" s="2">
-        <v>0.28023597060926703</v>
+        <v>0.91413772500687795</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>62</v>
+        <v>336</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="2">
-        <v>0.70994477938834299</v>
+        <v>8.6372432368955601E-2</v>
       </c>
       <c r="D20" s="2">
-        <v>0.29005522061165601</v>
+        <v>0.91362756763104402</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <v>0.70820036920719098</v>
+        <v>8.7827184360941904E-2</v>
       </c>
       <c r="D21" s="2">
-        <v>0.29179963079280802</v>
+        <v>0.91217281563905805</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2">
-        <v>0.70668992579615797</v>
+        <v>9.0384901900281395E-2</v>
       </c>
       <c r="D22" s="2">
-        <v>0.29331007420384198</v>
+        <v>0.90961509809971797</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2">
-        <v>0.70495768466030795</v>
+        <v>9.2925509080634794E-2</v>
       </c>
       <c r="D23" s="2">
-        <v>0.295042315339691</v>
+        <v>0.90707449091936498</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2">
-        <v>0.69867962252586402</v>
+        <v>9.3575518763545598E-2</v>
       </c>
       <c r="D24" s="2">
-        <v>0.30132037747413498</v>
+        <v>0.90642448123645403</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>374</v>
+        <v>247</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2">
-        <v>0.69788228181596701</v>
+        <v>9.3970191702778594E-2</v>
       </c>
       <c r="D25" s="2">
-        <v>0.30211771818403199</v>
+        <v>0.90602980829722102</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>151</v>
+        <v>372</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="2">
-        <v>0.69769425226210302</v>
+        <v>9.4369067031179907E-2</v>
       </c>
       <c r="D26" s="2">
-        <v>0.30230574773789598</v>
+        <v>0.90563093296882002</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>344</v>
+        <v>152</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27" s="2">
-        <v>0.69665244823072903</v>
+        <v>9.6431120277745905E-2</v>
       </c>
       <c r="D27" s="2">
-        <v>0.30334755176926997</v>
+        <v>0.90356887972225397</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2">
-        <v>0.69629452308208795</v>
+        <v>9.9027356285356596E-2</v>
       </c>
       <c r="D28" s="2">
-        <v>0.303705476917911</v>
+        <v>0.90097264371464303</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2">
-        <v>0.69551089254609799</v>
+        <v>9.9194297389389702E-2</v>
       </c>
       <c r="D29" s="2">
-        <v>0.30448910745390101</v>
+        <v>0.90080570261060999</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30" s="2">
-        <v>0.69092089518739497</v>
+        <v>0.100125151845101</v>
       </c>
       <c r="D30" s="2">
-        <v>0.30907910481260398</v>
+        <v>0.89987484815489804</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2">
-        <v>0.68912603776733605</v>
+        <v>0.100761668496054</v>
       </c>
       <c r="D31" s="2">
-        <v>0.310873962232663</v>
+        <v>0.89923833150394505</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2">
-        <v>0.68414390250879997</v>
+        <v>0.101896343794128</v>
       </c>
       <c r="D32" s="2">
-        <v>0.31585609749119897</v>
+        <v>0.89810365620587096</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" s="2">
-        <v>0.68039890368967304</v>
+        <v>0.102903754003495</v>
       </c>
       <c r="D33" s="2">
-        <v>0.31960109631032602</v>
+        <v>0.89709624599650395</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="2">
-        <v>0.67682613641658396</v>
+        <v>0.107324056404802</v>
       </c>
       <c r="D34" s="2">
-        <v>0.32317386358341499</v>
+        <v>0.89267594359519697</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2">
-        <v>0.66865401022957904</v>
+        <v>0.107358052943587</v>
       </c>
       <c r="D35" s="2">
-        <v>0.33134598977042001</v>
+        <v>0.89264194705641298</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>143</v>
+        <v>392</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2">
-        <v>0.66650289179223299</v>
+        <v>0.108165510067983</v>
       </c>
       <c r="D36" s="2">
-        <v>0.33349710820776601</v>
+        <v>0.89183448993201597</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" s="2">
-        <v>0.65975580911763299</v>
+        <v>0.108488790967656</v>
       </c>
       <c r="D37" s="2">
-        <v>0.34024419088236602</v>
+        <v>0.89151120903234304</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38" s="2">
-        <v>0.65950496640613998</v>
+        <v>0.11000390642123201</v>
       </c>
       <c r="D38" s="2">
-        <v>0.34049503359385902</v>
+        <v>0.88999609357876697</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" s="2">
-        <v>0.65647768033153198</v>
+        <v>0.11004715587545599</v>
       </c>
       <c r="D39" s="2">
-        <v>0.34352231966846702</v>
+        <v>0.88995284412454301</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>288</v>
+        <v>33</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2">
-        <v>0.65339672797952197</v>
+        <v>0.11154210066959699</v>
       </c>
       <c r="D40" s="2">
-        <v>0.34660327202047703</v>
+        <v>0.88845789933040198</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>307</v>
+        <v>37</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2">
-        <v>0.65194753076888401</v>
+        <v>0.112465090885733</v>
       </c>
       <c r="D41" s="2">
-        <v>0.34805246923111499</v>
+        <v>0.88753490911426602</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" s="2">
-        <v>0.64118633775858003</v>
+        <v>0.11363577711256199</v>
       </c>
       <c r="D42" s="2">
-        <v>0.35881366224141897</v>
+        <v>0.88636422288743699</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" s="2">
-        <v>0.63542216780036598</v>
+        <v>0.11366976429652299</v>
       </c>
       <c r="D43" s="2">
-        <v>0.36457783219963302</v>
+        <v>0.88633023570347602</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>3</v>
+        <v>396</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44" s="2">
-        <v>0.62976815584399404</v>
+        <v>0.113932462611348</v>
       </c>
       <c r="D44" s="2">
-        <v>0.37023184415600502</v>
+        <v>0.88606753738865096</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>389</v>
+        <v>168</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45" s="2">
-        <v>0.62624388458754698</v>
+        <v>0.11474333455334999</v>
       </c>
       <c r="D45" s="2">
-        <v>0.37375611541245202</v>
+        <v>0.88525666544664905</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>41</v>
+        <v>221</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>0.62488082507515696</v>
+        <v>0.114818543076169</v>
       </c>
       <c r="D46" s="2">
-        <v>0.37511917492484198</v>
+        <v>0.88518145692382999</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2">
-        <v>0.61914961331369101</v>
+        <v>0.115073327708979</v>
       </c>
       <c r="D47" s="2">
-        <v>0.380850386686308</v>
+        <v>0.88492667229101996</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>329</v>
+        <v>204</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2">
-        <v>0.61796354702745404</v>
+        <v>0.11670704173786001</v>
       </c>
       <c r="D48" s="2">
-        <v>0.38203645297254502</v>
+        <v>0.88329295826213905</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49" s="2">
-        <v>0.61727408366533698</v>
+        <v>0.116923082189252</v>
       </c>
       <c r="D49" s="2">
-        <v>0.38272591633466202</v>
+        <v>0.88307691781074704</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>399</v>
+        <v>140</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="2">
-        <v>0.61225365250215802</v>
+        <v>0.117280992114618</v>
       </c>
       <c r="D50" s="2">
-        <v>0.38774634749784098</v>
+        <v>0.88271900788538105</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2">
-        <v>0.60562783860859004</v>
+        <v>0.117609338436776</v>
       </c>
       <c r="D51" s="2">
-        <v>0.39437216139140902</v>
+        <v>0.88239066156322299</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52" s="2">
-        <v>0.60165637151364404</v>
+        <v>0.118420113216181</v>
       </c>
       <c r="D52" s="2">
-        <v>0.39834362848635502</v>
+        <v>0.88157988678381805</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" s="2">
-        <v>0.59835038011520503</v>
+        <v>0.11888060067003201</v>
       </c>
       <c r="D53" s="2">
-        <v>0.40164961988479497</v>
+        <v>0.88111939932996697</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>365</v>
+        <v>185</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54" s="2">
-        <v>0.59699831635998601</v>
+        <v>0.121533068769257</v>
       </c>
       <c r="D54" s="2">
-        <v>0.40300168364001299</v>
+        <v>0.87846693123074204</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="2">
-        <v>0.58857271255664101</v>
+        <v>0.122263799627587</v>
       </c>
       <c r="D55" s="2">
-        <v>0.41142728744335799</v>
+        <v>0.87773620037241196</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>32</v>
+        <v>311</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="2">
-        <v>0.58764472458003303</v>
+        <v>0.123798192581082</v>
       </c>
       <c r="D56" s="2">
-        <v>0.41235527541996603</v>
+        <v>0.87620180741891696</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="2">
-        <v>0.58668245911982098</v>
+        <v>0.124641159433229</v>
       </c>
       <c r="D57" s="2">
-        <v>0.41331754088017802</v>
+        <v>0.87535884056677005</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="2">
-        <v>0.58372538605829905</v>
+        <v>0.12522590979151499</v>
       </c>
       <c r="D58" s="2">
-        <v>0.41627461394170001</v>
+        <v>0.87477409020848496</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>282</v>
+        <v>367</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="2">
-        <v>0.581315980488193</v>
+        <v>0.12787577977477699</v>
       </c>
       <c r="D59" s="2">
-        <v>0.418684019511806</v>
+        <v>0.87212422022522196</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>327</v>
+        <v>23</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" s="2">
-        <v>0.57363821820748795</v>
+        <v>0.12814770184327301</v>
       </c>
       <c r="D60" s="2">
-        <v>0.426361781792512</v>
+        <v>0.87185229815672605</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2">
-        <v>0.57297449365773701</v>
+        <v>0.130388099956985</v>
       </c>
       <c r="D61" s="2">
-        <v>0.42702550634226299</v>
+        <v>0.86961190004301403</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2">
-        <v>0.57251257493956198</v>
+        <v>0.13108982553902301</v>
       </c>
       <c r="D62" s="2">
-        <v>0.42748742506043702</v>
+        <v>0.86891017446097596</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="2">
-        <v>0.57189629354016902</v>
+        <v>0.132515134311087</v>
       </c>
       <c r="D63" s="2">
-        <v>0.42810370645982998</v>
+        <v>0.86748486568891203</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64" s="2">
-        <v>0.569553228035239</v>
+        <v>0.13401507233370399</v>
       </c>
       <c r="D64" s="2">
-        <v>0.43044677196476</v>
+        <v>0.86598492766629498</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>155</v>
+        <v>388</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="2">
-        <v>0.56842974929308798</v>
+        <v>0.134462758336855</v>
       </c>
       <c r="D65" s="2">
-        <v>0.43157025070691102</v>
+        <v>0.86553724166314405</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" s="2">
-        <v>0.56585200155120496</v>
+        <v>0.13460563458031799</v>
       </c>
       <c r="D66" s="2">
-        <v>0.43414799844879398</v>
+        <v>0.86539436541968096</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" s="2">
-        <v>0.56409911280301706</v>
+        <v>0.13509044679975901</v>
       </c>
       <c r="D67" s="2">
-        <v>0.435900887196982</v>
+        <v>0.86490955320023999</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>120</v>
+        <v>394</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="2">
-        <v>0.56240842927651002</v>
+        <v>0.135367077456225</v>
       </c>
       <c r="D68" s="2">
-        <v>0.43759157072348898</v>
+        <v>0.864632922543774</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>272</v>
+        <v>85</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" s="2">
-        <v>0.55755742041737399</v>
+        <v>0.13830757054399101</v>
       </c>
       <c r="D69" s="2">
-        <v>0.44244257958262501</v>
+        <v>0.86169242945600799</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="2">
-        <v>0.55746729042809795</v>
+        <v>0.13865003659863501</v>
       </c>
       <c r="D70" s="2">
-        <v>0.442532709571901</v>
+        <v>0.86134996340136405</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="2">
-        <v>0.55408984271941697</v>
+        <v>0.14086257286939299</v>
       </c>
       <c r="D71" s="2">
-        <v>0.44591015728058198</v>
+        <v>0.85913742713060604</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="2">
-        <v>0.55402137857425005</v>
+        <v>0.14317247958892301</v>
       </c>
       <c r="D72" s="2">
-        <v>0.44597862142574901</v>
+        <v>0.85682752041107602</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73" s="2">
-        <v>0.55328556234154003</v>
+        <v>0.14433862793601299</v>
       </c>
       <c r="D73" s="2">
-        <v>0.44671443765845897</v>
+        <v>0.85566137206398596</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="2">
-        <v>0.54962624187008802</v>
+        <v>0.14435823152301699</v>
       </c>
       <c r="D74" s="2">
-        <v>0.45037375812991098</v>
+        <v>0.85564176847698203</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>347</v>
+        <v>9</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="2">
-        <v>0.549494286802094</v>
+        <v>0.144444899221119</v>
       </c>
       <c r="D75" s="2">
-        <v>0.450505713197905</v>
+        <v>0.85555510077887997</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76" s="2">
-        <v>0.54661961512289503</v>
+        <v>0.14578443815223799</v>
       </c>
       <c r="D76" s="2">
-        <v>0.45338038487710403</v>
+        <v>0.85421556184776104</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" s="2">
-        <v>0.54223416007430103</v>
+        <v>0.14627891227098699</v>
       </c>
       <c r="D77" s="2">
-        <v>0.45776583992569803</v>
+        <v>0.85372108772901201</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>53</v>
+        <v>290</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2">
-        <v>0.53799642141559001</v>
+        <v>0.148766680498265</v>
       </c>
       <c r="D78" s="2">
-        <v>0.46200357858440899</v>
+        <v>0.85123331950173398</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79" s="2">
-        <v>0.53400946481075595</v>
+        <v>0.149106990034095</v>
       </c>
       <c r="D79" s="2">
-        <v>0.46599053518924299</v>
+        <v>0.850893009965904</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="2">
-        <v>0.53240914966711295</v>
+        <v>0.15182142614027</v>
       </c>
       <c r="D80" s="2">
-        <v>0.467590850332886</v>
+        <v>0.84817857385972895</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>385</v>
+        <v>100</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81" s="2">
-        <v>0.52552482761053498</v>
+        <v>0.153928066967398</v>
       </c>
       <c r="D81" s="2">
-        <v>0.47447517238946402</v>
+        <v>0.84607193303260098</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82" s="2">
-        <v>0.52415741302443397</v>
+        <v>0.15468352469237001</v>
       </c>
       <c r="D82" s="2">
-        <v>0.47584258697556497</v>
+        <v>0.84531647530762899</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83" s="2">
-        <v>0.51899216178449803</v>
+        <v>0.155593233054059</v>
       </c>
       <c r="D83" s="2">
-        <v>0.48100783821550103</v>
+        <v>0.84440676694593997</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>363</v>
+        <v>148</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" s="2">
-        <v>0.51524994677824398</v>
+        <v>0.15664168779430901</v>
       </c>
       <c r="D84" s="2">
-        <v>0.48475005322175502</v>
+        <v>0.84335831220569002</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>6</v>
+        <v>266</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85" s="2">
-        <v>0.51442454871687004</v>
+        <v>0.158637346655433</v>
       </c>
       <c r="D85" s="2">
-        <v>0.48557545128312901</v>
+        <v>0.84136265334456595</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" s="2">
-        <v>0.51381634828274703</v>
+        <v>0.16126414372843301</v>
       </c>
       <c r="D86" s="2">
-        <v>0.48618365171725197</v>
+        <v>0.83873585627156699</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>355</v>
+        <v>192</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" s="2">
-        <v>0.51089785586324499</v>
+        <v>0.16257984272083301</v>
       </c>
       <c r="D87" s="2">
-        <v>0.48910214413675401</v>
+        <v>0.83742015727916597</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="2">
-        <v>0.50713081304568297</v>
+        <v>0.162758664718509</v>
       </c>
       <c r="D88" s="2">
-        <v>0.49286918695431597</v>
+        <v>0.83724133528149003</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>322</v>
+        <v>126</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="2">
-        <v>0.50677657054531899</v>
+        <v>0.164858029819788</v>
       </c>
       <c r="D89" s="2">
-        <v>0.49322342945468001</v>
+        <v>0.83514197018021097</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" s="2">
-        <v>0.50387210407711203</v>
+        <v>0.164910788500475</v>
       </c>
       <c r="D90" s="2">
-        <v>0.49612789592288797</v>
+        <v>0.83508921149952398</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>29</v>
+        <v>345</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91" s="2">
-        <v>0.50151153933103498</v>
+        <v>0.16639470142360299</v>
       </c>
       <c r="D91" s="2">
-        <v>0.49848846066896402</v>
+        <v>0.83360529857639598</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92" s="2">
-        <v>0.50028208072713698</v>
+        <v>0.16698835353001401</v>
       </c>
       <c r="D92" s="2">
-        <v>0.49971791927286202</v>
+        <v>0.83301164646998505</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>196</v>
+        <v>287</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" s="2">
-        <v>0.49996779850686501</v>
+        <v>0.16712433999908299</v>
       </c>
       <c r="D93" s="2">
-        <v>0.50003220149313399</v>
+        <v>0.83287566000091595</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -9310,16 +9310,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94" s="2">
-        <v>0.49893371692821997</v>
+        <v>0.16869384867392501</v>
       </c>
       <c r="D94" s="2">
-        <v>0.50106628307177903</v>
+        <v>0.83130615132607399</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -9327,16 +9327,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" s="2">
-        <v>0.492064556855701</v>
+        <v>0.16894138655559199</v>
       </c>
       <c r="D95" s="2">
-        <v>0.50793544314429795</v>
+        <v>0.83105861344440801</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -9344,16 +9344,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96" s="2">
-        <v>0.49115954554803998</v>
+        <v>0.16978387567657399</v>
       </c>
       <c r="D96" s="2">
-        <v>0.50884045445195902</v>
+        <v>0.83021612432342495</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -9361,16 +9361,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97" s="2">
-        <v>0.48924707307172799</v>
+        <v>0.17013659553534799</v>
       </c>
       <c r="D97" s="2">
-        <v>0.51075292692827101</v>
+        <v>0.82986340446465101</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -9378,16 +9378,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" s="2">
-        <v>0.48579403022614398</v>
+        <v>0.172363063204619</v>
       </c>
       <c r="D98" s="2">
-        <v>0.51420596977385502</v>
+        <v>0.82763693679538097</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -9395,16 +9395,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>10</v>
+        <v>213</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99" s="2">
-        <v>0.484814554431381</v>
+        <v>0.172493215668758</v>
       </c>
       <c r="D99" s="2">
-        <v>0.51518544556861801</v>
+        <v>0.82750678433124103</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -9412,16 +9412,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100" s="2">
-        <v>0.48293966373122399</v>
+        <v>0.17295166446565099</v>
       </c>
       <c r="D100" s="2">
-        <v>0.51706033626877501</v>
+        <v>0.82704833553434798</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -9429,16 +9429,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>239</v>
+        <v>351</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" s="2">
-        <v>0.479211650366479</v>
+        <v>0.17484992424090801</v>
       </c>
       <c r="D101" s="2">
-        <v>0.52078834963352005</v>
+        <v>0.82515007575909105</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -9446,16 +9446,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" s="2">
-        <v>0.47917879496022198</v>
+        <v>0.17563520788711501</v>
       </c>
       <c r="D102" s="2">
-        <v>0.52082120503977702</v>
+        <v>0.82436479211288405</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -9463,16 +9463,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103" s="2">
-        <v>0.47817569459750597</v>
+        <v>0.17624644158295</v>
       </c>
       <c r="D103" s="2">
-        <v>0.52182430540249303</v>
+        <v>0.823753558417049</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -9480,16 +9480,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>251</v>
+        <v>306</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" s="2">
-        <v>0.47736289163957002</v>
+        <v>0.17751077104589399</v>
       </c>
       <c r="D104" s="2">
-        <v>0.52263710836042898</v>
+        <v>0.82248922895410503</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -9497,16 +9497,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105" s="2">
-        <v>0.47569637223121702</v>
+        <v>0.17775590926644699</v>
       </c>
       <c r="D105" s="2">
-        <v>0.52430362776878203</v>
+        <v>0.82224409073355298</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -9514,16 +9514,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>360</v>
+        <v>116</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106" s="2">
-        <v>0.47309116483942099</v>
+        <v>0.182977159439841</v>
       </c>
       <c r="D106" s="2">
-        <v>0.52690883516057796</v>
+        <v>0.81702284056015795</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -9531,16 +9531,16 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107" s="2">
-        <v>0.46684649874114398</v>
+        <v>0.18479289542483801</v>
       </c>
       <c r="D107" s="2">
-        <v>0.53315350125885497</v>
+        <v>0.81520710457516199</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -9548,16 +9548,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108" s="2">
-        <v>0.464936477228028</v>
+        <v>0.18485029987608001</v>
       </c>
       <c r="D108" s="2">
-        <v>0.535063522771971</v>
+        <v>0.81514970012391896</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -9565,16 +9565,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" s="2">
-        <v>0.46355419166759299</v>
+        <v>0.18539601473359399</v>
       </c>
       <c r="D109" s="2">
-        <v>0.53644580833240596</v>
+        <v>0.81460398526640498</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -9582,16 +9582,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>397</v>
+        <v>50</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2">
-        <v>0.46133435036995002</v>
+        <v>0.186834984626019</v>
       </c>
       <c r="D110" s="2">
-        <v>0.53866564963004904</v>
+        <v>0.813165015373981</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -9599,16 +9599,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" s="2">
-        <v>0.460815389856161</v>
+        <v>0.187990830009645</v>
       </c>
       <c r="D111" s="2">
-        <v>0.53918461014383801</v>
+        <v>0.812009169990354</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -9616,16 +9616,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>315</v>
+        <v>35</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112" s="2">
-        <v>0.460246149425933</v>
+        <v>0.18906972146261999</v>
       </c>
       <c r="D112" s="2">
-        <v>0.539753850574066</v>
+        <v>0.81093027853737898</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -9633,16 +9633,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>313</v>
+        <v>123</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="2">
-        <v>0.46016692119865099</v>
+        <v>0.19250822863575001</v>
       </c>
       <c r="D113" s="2">
-        <v>0.53983307880134801</v>
+        <v>0.80749177136424899</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -9650,16 +9650,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" s="2">
-        <v>0.45837929244292203</v>
+        <v>0.192981801475509</v>
       </c>
       <c r="D114" s="2">
-        <v>0.54162070755707703</v>
+        <v>0.80701819852448997</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -9667,16 +9667,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115" s="2">
-        <v>0.45580682132009398</v>
+        <v>0.196165976432077</v>
       </c>
       <c r="D115" s="2">
-        <v>0.54419317867990502</v>
+        <v>0.803834023567922</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -9684,16 +9684,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116" s="2">
-        <v>0.45461313661081898</v>
+        <v>0.196580855402927</v>
       </c>
       <c r="D116" s="2">
-        <v>0.54538686338917997</v>
+        <v>0.80341914459707198</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -9701,16 +9701,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117" s="2">
-        <v>0.45414094314373399</v>
+        <v>0.19860742269130699</v>
       </c>
       <c r="D117" s="2">
-        <v>0.54585905685626501</v>
+        <v>0.80139257730869196</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -9718,16 +9718,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>390</v>
+        <v>321</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" s="2">
-        <v>0.44999501854929402</v>
+        <v>0.20004736023532599</v>
       </c>
       <c r="D118" s="2">
-        <v>0.55000498145070598</v>
+        <v>0.79995263976467301</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -9735,16 +9735,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" s="2">
-        <v>0.44501333059346398</v>
+        <v>0.20026538233142899</v>
       </c>
       <c r="D119" s="2">
-        <v>0.55498666940653496</v>
+        <v>0.79973461766857001</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -9752,16 +9752,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>334</v>
+        <v>70</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" s="2">
-        <v>0.443993155584614</v>
+        <v>0.20754281370403799</v>
       </c>
       <c r="D120" s="2">
-        <v>0.55600684441538495</v>
+        <v>0.79245718629596096</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -9769,16 +9769,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>328</v>
+        <v>250</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121" s="2">
-        <v>0.43757778714511097</v>
+        <v>0.209999852324256</v>
       </c>
       <c r="D121" s="2">
-        <v>0.56242221285488803</v>
+        <v>0.790000147675743</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -9786,16 +9786,16 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" s="2">
-        <v>0.43517222180315002</v>
+        <v>0.21123644945783099</v>
       </c>
       <c r="D122" s="2">
-        <v>0.56482777819684904</v>
+        <v>0.78876355054216796</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -9803,16 +9803,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>24</v>
+        <v>391</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" s="2">
-        <v>0.43409471053679699</v>
+        <v>0.213201578455189</v>
       </c>
       <c r="D123" s="2">
-        <v>0.56590528946320195</v>
+        <v>0.78679842154480994</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -9820,16 +9820,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124" s="2">
-        <v>0.43237789482669697</v>
+        <v>0.21418280292561201</v>
       </c>
       <c r="D124" s="2">
-        <v>0.56762210517330203</v>
+        <v>0.78581719707438702</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -9837,16 +9837,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>63</v>
+        <v>362</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125" s="2">
-        <v>0.431198767000112</v>
+        <v>0.21564774482812299</v>
       </c>
       <c r="D125" s="2">
-        <v>0.56880123299988705</v>
+        <v>0.78435225517187601</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -9854,16 +9854,16 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>339</v>
+        <v>95</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" s="2">
-        <v>0.42802902753623201</v>
+        <v>0.21634993691925999</v>
       </c>
       <c r="D126" s="2">
-        <v>0.57197097246376705</v>
+        <v>0.78365006308073903</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -9871,16 +9871,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2">
-        <v>0.42105988515153397</v>
+        <v>0.21638057887512099</v>
       </c>
       <c r="D127" s="2">
-        <v>0.57894011484846497</v>
+        <v>0.78361942112487804</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -9888,16 +9888,16 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" s="2">
-        <v>0.420856120362121</v>
+        <v>0.218847660579087</v>
       </c>
       <c r="D128" s="2">
-        <v>0.57914387963787795</v>
+        <v>0.781152339420912</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -9905,16 +9905,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" s="2">
-        <v>0.42084065872179399</v>
+        <v>0.21891851682114299</v>
       </c>
       <c r="D129" s="2">
-        <v>0.57915934127820501</v>
+        <v>0.78108148317885595</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -9922,16 +9922,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>387</v>
+        <v>107</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" s="2">
-        <v>0.42061007803986</v>
+        <v>0.21920465098860301</v>
       </c>
       <c r="D130" s="2">
-        <v>0.57938992196013905</v>
+        <v>0.78079534901139602</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -9939,16 +9939,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131" s="2">
-        <v>0.41958265785267901</v>
+        <v>0.221082797625095</v>
       </c>
       <c r="D131" s="2">
-        <v>0.58041734214731999</v>
+        <v>0.77891720237490403</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -9956,16 +9956,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>188</v>
+        <v>380</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132" s="2">
-        <v>0.419284441852046</v>
+        <v>0.221651020308201</v>
       </c>
       <c r="D132" s="2">
-        <v>0.58071555814795295</v>
+        <v>0.77834897969179895</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -9973,16 +9973,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133" s="2">
-        <v>0.41692655978883802</v>
+        <v>0.222126658861098</v>
       </c>
       <c r="D133" s="2">
-        <v>0.58307344021116103</v>
+        <v>0.77787334113890105</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -9990,16 +9990,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" s="2">
-        <v>0.41506780110979002</v>
+        <v>0.226095186262498</v>
       </c>
       <c r="D134" s="2">
-        <v>0.58493219889020898</v>
+        <v>0.77390481373750097</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -10007,16 +10007,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>26</v>
+        <v>301</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135" s="2">
-        <v>0.41040746297325498</v>
+        <v>0.228181169590225</v>
       </c>
       <c r="D135" s="2">
-        <v>0.58959253702674397</v>
+        <v>0.77181883040977395</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -10024,16 +10024,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136" s="2">
-        <v>0.41009599632030103</v>
+        <v>0.228282541273229</v>
       </c>
       <c r="D136" s="2">
-        <v>0.58990400367969797</v>
+        <v>0.77171745872677</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -10041,16 +10041,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>312</v>
+        <v>218</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137" s="2">
-        <v>0.40983085955818799</v>
+        <v>0.229074471093861</v>
       </c>
       <c r="D137" s="2">
-        <v>0.59016914044181101</v>
+        <v>0.77092552890613897</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -10058,16 +10058,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>300</v>
+        <v>205</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" s="2">
-        <v>0.40703652695507297</v>
+        <v>0.231983282287378</v>
       </c>
       <c r="D138" s="2">
-        <v>0.59296347304492603</v>
+        <v>0.76801671771262103</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -10075,16 +10075,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139" s="2">
-        <v>0.40677009417979199</v>
+        <v>0.232119132161165</v>
       </c>
       <c r="D139" s="2">
-        <v>0.59322990582020696</v>
+        <v>0.76788086783883402</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -10092,16 +10092,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140" s="2">
-        <v>0.406092544147795</v>
+        <v>0.23337679864709401</v>
       </c>
       <c r="D140" s="2">
-        <v>0.59390745585220395</v>
+        <v>0.76662320135290596</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -10109,16 +10109,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>96</v>
+        <v>310</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141" s="2">
-        <v>0.404889617997508</v>
+        <v>0.234067189161943</v>
       </c>
       <c r="D141" s="2">
-        <v>0.595110382002491</v>
+        <v>0.76593281083805598</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -10126,16 +10126,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" s="2">
-        <v>0.40467611180049401</v>
+        <v>0.23777838029922499</v>
       </c>
       <c r="D142" s="2">
-        <v>0.59532388819950499</v>
+        <v>0.76222161970077396</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -10143,16 +10143,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>256</v>
+        <v>333</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143" s="2">
-        <v>0.403148640243434</v>
+        <v>0.24004294574812199</v>
       </c>
       <c r="D143" s="2">
-        <v>0.596851359756565</v>
+        <v>0.75995705425187798</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -10160,16 +10160,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144" s="2">
-        <v>0.40276566195411301</v>
+        <v>0.241058229569376</v>
       </c>
       <c r="D144" s="2">
-        <v>0.59723433804588599</v>
+        <v>0.75894177043062305</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -10177,16 +10177,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>386</v>
+        <v>172</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2">
-        <v>0.39290176906390001</v>
+        <v>0.242775916142313</v>
       </c>
       <c r="D145" s="2">
-        <v>0.60709823093609905</v>
+        <v>0.75722408385768603</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -10194,16 +10194,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" s="2">
-        <v>0.39271216693817601</v>
+        <v>0.24315245187682499</v>
       </c>
       <c r="D146" s="2">
-        <v>0.60728783306182299</v>
+        <v>0.75684754812317401</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -10211,16 +10211,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" s="2">
-        <v>0.38965652511280502</v>
+        <v>0.24505919629988099</v>
       </c>
       <c r="D147" s="2">
-        <v>0.61034347488719398</v>
+        <v>0.75494080370011796</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -10228,16 +10228,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" s="2">
-        <v>0.38915530580473101</v>
+        <v>0.245762787463981</v>
       </c>
       <c r="D148" s="2">
-        <v>0.61084469419526799</v>
+        <v>0.75423721253601805</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -10245,16 +10245,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>86</v>
+        <v>228</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149" s="2">
-        <v>0.38874413422845</v>
+        <v>0.24688002564640901</v>
       </c>
       <c r="D149" s="2">
-        <v>0.611255865771549</v>
+        <v>0.75311997435359002</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -10262,16 +10262,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C150" s="2">
-        <v>0.38412705961094001</v>
+        <v>0.24738606058746601</v>
       </c>
       <c r="D150" s="2">
-        <v>0.61587294038905904</v>
+        <v>0.75261393941253296</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -10279,16 +10279,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151" s="2">
-        <v>0.38408044177670497</v>
+        <v>0.24920147230790801</v>
       </c>
       <c r="D151" s="2">
-        <v>0.61591955822329403</v>
+        <v>0.75079852769209099</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -10296,16 +10296,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>231</v>
+        <v>303</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152" s="2">
-        <v>0.38145424209809498</v>
+        <v>0.25084564556503902</v>
       </c>
       <c r="D152" s="2">
-        <v>0.61854575790190403</v>
+        <v>0.74915435443496003</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -10313,16 +10313,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153" s="2">
-        <v>0.37900338060171501</v>
+        <v>0.251155272837155</v>
       </c>
       <c r="D153" s="2">
-        <v>0.62099661939828399</v>
+        <v>0.748844727162844</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -10330,16 +10330,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>119</v>
+        <v>240</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" s="2">
-        <v>0.37614659168917403</v>
+        <v>0.25358619599469401</v>
       </c>
       <c r="D154" s="2">
-        <v>0.62385340831082503</v>
+        <v>0.74641380400530499</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -10347,16 +10347,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="B155">
         <v>1</v>
       </c>
       <c r="C155" s="2">
-        <v>0.37533076811223998</v>
+        <v>0.25445357710754901</v>
       </c>
       <c r="D155" s="2">
-        <v>0.62466923188775902</v>
+        <v>0.74554642289244999</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -10364,16 +10364,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156" s="2">
-        <v>0.37480688782848398</v>
+        <v>0.25728858915584601</v>
       </c>
       <c r="D156" s="2">
-        <v>0.62519311217151496</v>
+        <v>0.74271141084415304</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10381,16 +10381,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>323</v>
+        <v>88</v>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157" s="2">
-        <v>0.37448994398639801</v>
+        <v>0.25779861717860603</v>
       </c>
       <c r="D157" s="2">
-        <v>0.62551005601360199</v>
+        <v>0.74220138282139303</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -10398,16 +10398,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>2</v>
+        <v>216</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" s="2">
-        <v>0.37313482853214602</v>
+        <v>0.258761506146721</v>
       </c>
       <c r="D158" s="2">
-        <v>0.62686517146785303</v>
+        <v>0.741238493853278</v>
       </c>
       <c r="E158">
         <v>1</v>
@@ -10415,16 +10415,16 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>214</v>
+        <v>378</v>
       </c>
       <c r="B159">
         <v>1</v>
       </c>
       <c r="C159" s="2">
-        <v>0.37246639873509901</v>
+        <v>0.25941096366542399</v>
       </c>
       <c r="D159" s="2">
-        <v>0.62753360126489999</v>
+        <v>0.74058903633457496</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -10432,16 +10432,16 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>174</v>
+        <v>284</v>
       </c>
       <c r="B160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" s="2">
-        <v>0.36717398424111303</v>
+        <v>0.26099325252351802</v>
       </c>
       <c r="D160" s="2">
-        <v>0.63282601575888597</v>
+        <v>0.73900674747648099</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -10449,16 +10449,16 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="B161">
         <v>1</v>
       </c>
       <c r="C161" s="2">
-        <v>0.36519773535169497</v>
+        <v>0.26392854987696102</v>
       </c>
       <c r="D161" s="2">
-        <v>0.63480226464830403</v>
+        <v>0.73607145012303798</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -10466,16 +10466,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>383</v>
+        <v>68</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
       <c r="C162" s="2">
-        <v>0.36242433927902501</v>
+        <v>0.26432012208739603</v>
       </c>
       <c r="D162" s="2">
-        <v>0.63757566072097405</v>
+        <v>0.73567987791260303</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -10483,16 +10483,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>206</v>
+        <v>337</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163" s="2">
-        <v>0.36187059885015399</v>
+        <v>0.26495177030531097</v>
       </c>
       <c r="D163" s="2">
-        <v>0.63812940114984495</v>
+        <v>0.73504822969468797</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -10500,16 +10500,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>381</v>
+        <v>137</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164" s="2">
-        <v>0.360801501137202</v>
+        <v>0.26886434325654102</v>
       </c>
       <c r="D164" s="2">
-        <v>0.639198498862797</v>
+        <v>0.73113565674345804</v>
       </c>
       <c r="E164">
         <v>1</v>
@@ -10517,16 +10517,16 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>129</v>
+        <v>298</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165" s="2">
-        <v>0.360303582094679</v>
+        <v>0.26898675342452699</v>
       </c>
       <c r="D165" s="2">
-        <v>0.63969641790532095</v>
+        <v>0.73101324657547195</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -10534,16 +10534,16 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166" s="2">
-        <v>0.36020230592508801</v>
+        <v>0.27063113603419198</v>
       </c>
       <c r="D166" s="2">
-        <v>0.63979769407491105</v>
+        <v>0.72936886396580702</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -10551,16 +10551,16 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167" s="2">
-        <v>0.35882112486155499</v>
+        <v>0.27158049470731899</v>
       </c>
       <c r="D167" s="2">
-        <v>0.64117887513844496</v>
+        <v>0.72841950529267996</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10568,16 +10568,16 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168" s="2">
-        <v>0.35504389074395398</v>
+        <v>0.27253556424993602</v>
       </c>
       <c r="D168" s="2">
-        <v>0.64495610925604496</v>
+        <v>0.72746443575006303</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -10585,16 +10585,16 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169" s="2">
-        <v>0.35419913857142499</v>
+        <v>0.27318290242094601</v>
       </c>
       <c r="D169" s="2">
-        <v>0.64580086142857396</v>
+        <v>0.726817097579053</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -10602,16 +10602,16 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" s="2">
-        <v>0.351634587736596</v>
+        <v>0.27374413181205498</v>
       </c>
       <c r="D170" s="2">
-        <v>0.64836541226340305</v>
+        <v>0.72625586818794396</v>
       </c>
       <c r="E170">
         <v>1</v>
@@ -10619,16 +10619,16 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" s="2">
-        <v>0.35022183900291098</v>
+        <v>0.27554670281010102</v>
       </c>
       <c r="D171" s="2">
-        <v>0.64977816099708796</v>
+        <v>0.72445329718989804</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -10636,16 +10636,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>366</v>
+        <v>47</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" s="2">
-        <v>0.34966680554516899</v>
+        <v>0.27710211064376999</v>
       </c>
       <c r="D172" s="2">
-        <v>0.65033319445482995</v>
+        <v>0.72289788935622901</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -10653,16 +10653,16 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>199</v>
+        <v>331</v>
       </c>
       <c r="B173">
         <v>1</v>
       </c>
       <c r="C173" s="2">
-        <v>0.34404270866895897</v>
+        <v>0.27781570733417399</v>
       </c>
       <c r="D173" s="2">
-        <v>0.65595729133103997</v>
+        <v>0.72218429266582496</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -10670,16 +10670,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="B174">
         <v>1</v>
       </c>
       <c r="C174" s="2">
-        <v>0.34179201865543501</v>
+        <v>0.28063172859399699</v>
       </c>
       <c r="D174" s="2">
-        <v>0.65820798134456404</v>
+        <v>0.71936827140600201</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -10687,16 +10687,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175" s="2">
-        <v>0.34036807528809898</v>
+        <v>0.28119678566501699</v>
       </c>
       <c r="D175" s="2">
-        <v>0.65963192471190002</v>
+        <v>0.71880321433498195</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -10704,16 +10704,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176" s="2">
-        <v>0.33953936742927499</v>
+        <v>0.28199995822201401</v>
       </c>
       <c r="D176" s="2">
-        <v>0.66046063257072396</v>
+        <v>0.71800004177798504</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -10721,16 +10721,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>320</v>
+        <v>219</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177" s="2">
-        <v>0.33683371706656301</v>
+        <v>0.28324976745032598</v>
       </c>
       <c r="D177" s="2">
-        <v>0.66316628293343605</v>
+        <v>0.71675023254967296</v>
       </c>
       <c r="E177">
         <v>1</v>
@@ -10738,16 +10738,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>69</v>
+        <v>207</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178" s="2">
-        <v>0.33531155423528902</v>
+        <v>0.28923921709920603</v>
       </c>
       <c r="D178" s="2">
-        <v>0.66468844576470998</v>
+        <v>0.71076078290079303</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -10755,16 +10755,16 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>217</v>
+        <v>395</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179" s="2">
-        <v>0.33397925673477202</v>
+        <v>0.28951606104317201</v>
       </c>
       <c r="D179" s="2">
-        <v>0.66602074326522798</v>
+        <v>0.71048393895682704</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -10772,16 +10772,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180" s="2">
-        <v>0.33316374142997002</v>
+        <v>0.29076737013153298</v>
       </c>
       <c r="D180" s="2">
-        <v>0.66683625857002904</v>
+        <v>0.70923262986846602</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -10789,16 +10789,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181">
-        <v>169</v>
+        <v>325</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181" s="2">
-        <v>0.33290418266782101</v>
+        <v>0.292362884790758</v>
       </c>
       <c r="D181" s="2">
-        <v>0.66709581733217804</v>
+        <v>0.707637115209241</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -10806,16 +10806,16 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182" s="2">
-        <v>0.33252591512111801</v>
+        <v>0.29244533845704701</v>
       </c>
       <c r="D182" s="2">
-        <v>0.66747408487888105</v>
+        <v>0.70755466154295199</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -10823,16 +10823,16 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183" s="2">
-        <v>0.33252195344361501</v>
+        <v>0.293192053362474</v>
       </c>
       <c r="D183" s="2">
-        <v>0.66747804655638399</v>
+        <v>0.706807946637525</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -10840,16 +10840,16 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184" s="2">
-        <v>0.33237817256942198</v>
+        <v>0.293774800162516</v>
       </c>
       <c r="D184" s="2">
-        <v>0.66762182743057696</v>
+        <v>0.706225199837483</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -10857,16 +10857,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B185">
         <v>1</v>
       </c>
       <c r="C185" s="2">
-        <v>0.33216164086719902</v>
+        <v>0.29630775275148502</v>
       </c>
       <c r="D185" s="2">
-        <v>0.66783835913279999</v>
+        <v>0.70369224724851398</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -10874,16 +10874,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" s="2">
-        <v>0.330051377715598</v>
+        <v>0.29756891371646099</v>
       </c>
       <c r="D186" s="2">
-        <v>0.669948622284401</v>
+        <v>0.70243108628353801</v>
       </c>
       <c r="E186">
         <v>1</v>
@@ -10891,16 +10891,16 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>249</v>
+        <v>375</v>
       </c>
       <c r="B187">
         <v>1</v>
       </c>
       <c r="C187" s="2">
-        <v>0.32990996893159502</v>
+        <v>0.29769343888509098</v>
       </c>
       <c r="D187" s="2">
-        <v>0.67009003106840404</v>
+        <v>0.70230656111490797</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -10908,16 +10908,16 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188" s="2">
-        <v>0.329647406718653</v>
+        <v>0.29925616136107702</v>
       </c>
       <c r="D188" s="2">
-        <v>0.670352593281346</v>
+        <v>0.70074383863892198</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -10925,16 +10925,16 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189" s="2">
-        <v>0.32715662493913</v>
+        <v>0.299860409460599</v>
       </c>
       <c r="D189" s="2">
-        <v>0.672843375060869</v>
+        <v>0.7001395905394</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -10942,16 +10942,16 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190" s="2">
-        <v>0.32678821604161501</v>
+        <v>0.30014057805655098</v>
       </c>
       <c r="D190" s="2">
-        <v>0.67321178395838399</v>
+        <v>0.69985942194344897</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -10959,16 +10959,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>193</v>
+        <v>348</v>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191" s="2">
-        <v>0.326231788050034</v>
+        <v>0.30046113046397699</v>
       </c>
       <c r="D191" s="2">
-        <v>0.67376821194996495</v>
+        <v>0.69953886953602196</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -10976,16 +10976,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" s="2">
-        <v>0.32354581702286</v>
+        <v>0.30070557484792598</v>
       </c>
       <c r="D192" s="2">
-        <v>0.676454182977139</v>
+        <v>0.69929442515207296</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -10993,16 +10993,16 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B193">
         <v>1</v>
       </c>
       <c r="C193" s="2">
-        <v>0.32335959722789098</v>
+        <v>0.30075960170344601</v>
       </c>
       <c r="D193" s="2">
-        <v>0.67664040277210802</v>
+        <v>0.69924039829655305</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -11010,16 +11010,16 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>382</v>
+        <v>48</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194" s="2">
-        <v>0.31942966400284201</v>
+        <v>0.30137524256895099</v>
       </c>
       <c r="D194" s="2">
-        <v>0.68057033599715799</v>
+        <v>0.69862475743104802</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -11027,16 +11027,16 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="B195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C195" s="2">
-        <v>0.317818971653546</v>
+        <v>0.30150861058802098</v>
       </c>
       <c r="D195" s="2">
-        <v>0.682181028346453</v>
+        <v>0.69849138941197897</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -11044,16 +11044,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>359</v>
+        <v>268</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" s="2">
-        <v>0.31730943432734798</v>
+        <v>0.30262440210914898</v>
       </c>
       <c r="D196" s="2">
-        <v>0.68269056567265196</v>
+        <v>0.69737559789085002</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -11061,16 +11061,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C197" s="2">
-        <v>0.31699005444084599</v>
+        <v>0.30646528367970399</v>
       </c>
       <c r="D197" s="2">
-        <v>0.68300994555915295</v>
+        <v>0.69353471632029495</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -11078,16 +11078,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198" s="2">
-        <v>0.31602341802245199</v>
+        <v>0.307490406676588</v>
       </c>
       <c r="D198" s="2">
-        <v>0.68397658197754696</v>
+        <v>0.692509593323411</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -11095,16 +11095,16 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C199" s="2">
-        <v>0.31571184900468202</v>
+        <v>0.30902042884405001</v>
       </c>
       <c r="D199" s="2">
-        <v>0.68428815099531703</v>
+        <v>0.69097957115594899</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -11112,16 +11112,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="B200">
         <v>1</v>
       </c>
       <c r="C200" s="2">
-        <v>0.31555514299339299</v>
+        <v>0.309704324365073</v>
       </c>
       <c r="D200" s="2">
-        <v>0.68444485700660596</v>
+        <v>0.690295675634926</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -11129,16 +11129,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201" s="2">
-        <v>0.31327244195659598</v>
+        <v>0.31176723546570501</v>
       </c>
       <c r="D201" s="2">
-        <v>0.68672755804340302</v>
+        <v>0.68823276453429405</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -11146,16 +11146,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202" s="2">
-        <v>0.31176723546570501</v>
+        <v>0.31327244195659598</v>
       </c>
       <c r="D202" s="2">
-        <v>0.68823276453429405</v>
+        <v>0.68672755804340302</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -11163,16 +11163,16 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203">
-        <v>373</v>
+        <v>200</v>
       </c>
       <c r="B203">
         <v>1</v>
       </c>
       <c r="C203" s="2">
-        <v>0.309704324365073</v>
+        <v>0.31555514299339299</v>
       </c>
       <c r="D203" s="2">
-        <v>0.690295675634926</v>
+        <v>0.68444485700660596</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -11180,16 +11180,16 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204" s="2">
-        <v>0.30902042884405001</v>
+        <v>0.31571184900468202</v>
       </c>
       <c r="D204" s="2">
-        <v>0.69097957115594899</v>
+        <v>0.68428815099531703</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -11197,16 +11197,16 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="B205">
         <v>1</v>
       </c>
       <c r="C205" s="2">
-        <v>0.307490406676588</v>
+        <v>0.31602341802245199</v>
       </c>
       <c r="D205" s="2">
-        <v>0.692509593323411</v>
+        <v>0.68397658197754696</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -11214,16 +11214,16 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" s="2">
-        <v>0.30646528367970399</v>
+        <v>0.31699005444084599</v>
       </c>
       <c r="D206" s="2">
-        <v>0.69353471632029495</v>
+        <v>0.68300994555915295</v>
       </c>
       <c r="E206">
         <v>1</v>
@@ -11231,16 +11231,16 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207">
-        <v>268</v>
+        <v>359</v>
       </c>
       <c r="B207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207" s="2">
-        <v>0.30262440210914898</v>
+        <v>0.31730943432734798</v>
       </c>
       <c r="D207" s="2">
-        <v>0.69737559789085002</v>
+        <v>0.68269056567265196</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -11248,16 +11248,16 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208">
-        <v>346</v>
+        <v>281</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208" s="2">
-        <v>0.30150861058802098</v>
+        <v>0.317818971653546</v>
       </c>
       <c r="D208" s="2">
-        <v>0.69849138941197897</v>
+        <v>0.682181028346453</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -11265,16 +11265,16 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209">
-        <v>48</v>
+        <v>382</v>
       </c>
       <c r="B209">
         <v>1</v>
       </c>
       <c r="C209" s="2">
-        <v>0.30137524256895099</v>
+        <v>0.31942966400284201</v>
       </c>
       <c r="D209" s="2">
-        <v>0.69862475743104802</v>
+        <v>0.68057033599715799</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -11282,16 +11282,16 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B210">
         <v>1</v>
       </c>
       <c r="C210" s="2">
-        <v>0.30075960170344601</v>
+        <v>0.32335959722789098</v>
       </c>
       <c r="D210" s="2">
-        <v>0.69924039829655305</v>
+        <v>0.67664040277210802</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -11299,16 +11299,16 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C211" s="2">
-        <v>0.30070557484792598</v>
+        <v>0.32354581702286</v>
       </c>
       <c r="D211" s="2">
-        <v>0.69929442515207296</v>
+        <v>0.676454182977139</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -11316,16 +11316,16 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212">
-        <v>348</v>
+        <v>193</v>
       </c>
       <c r="B212">
         <v>1</v>
       </c>
       <c r="C212" s="2">
-        <v>0.30046113046397699</v>
+        <v>0.326231788050034</v>
       </c>
       <c r="D212" s="2">
-        <v>0.69953886953602196</v>
+        <v>0.67376821194996495</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -11333,16 +11333,16 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="B213">
         <v>1</v>
       </c>
       <c r="C213" s="2">
-        <v>0.30014057805655098</v>
+        <v>0.32678821604161501</v>
       </c>
       <c r="D213" s="2">
-        <v>0.69985942194344897</v>
+        <v>0.67321178395838399</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -11350,16 +11350,16 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214" s="2">
-        <v>0.299860409460599</v>
+        <v>0.32715662493913</v>
       </c>
       <c r="D214" s="2">
-        <v>0.7001395905394</v>
+        <v>0.672843375060869</v>
       </c>
       <c r="E214">
         <v>1</v>
@@ -11367,16 +11367,16 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215">
-        <v>294</v>
+        <v>12</v>
       </c>
       <c r="B215">
         <v>1</v>
       </c>
       <c r="C215" s="2">
-        <v>0.29925616136107702</v>
+        <v>0.329647406718653</v>
       </c>
       <c r="D215" s="2">
-        <v>0.70074383863892198</v>
+        <v>0.670352593281346</v>
       </c>
       <c r="E215">
         <v>1</v>
@@ -11384,16 +11384,16 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216">
-        <v>375</v>
+        <v>249</v>
       </c>
       <c r="B216">
         <v>1</v>
       </c>
       <c r="C216" s="2">
-        <v>0.29769343888509098</v>
+        <v>0.32990996893159502</v>
       </c>
       <c r="D216" s="2">
-        <v>0.70230656111490797</v>
+        <v>0.67009003106840404</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -11401,16 +11401,16 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" s="2">
-        <v>0.29756891371646099</v>
+        <v>0.330051377715598</v>
       </c>
       <c r="D217" s="2">
-        <v>0.70243108628353801</v>
+        <v>0.669948622284401</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -11418,16 +11418,16 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B218">
         <v>1</v>
       </c>
       <c r="C218" s="2">
-        <v>0.29630775275148502</v>
+        <v>0.33216164086719902</v>
       </c>
       <c r="D218" s="2">
-        <v>0.70369224724851398</v>
+        <v>0.66783835913279999</v>
       </c>
       <c r="E218">
         <v>1</v>
@@ -11435,16 +11435,16 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="B219">
         <v>1</v>
       </c>
       <c r="C219" s="2">
-        <v>0.293774800162516</v>
+        <v>0.33237817256942198</v>
       </c>
       <c r="D219" s="2">
-        <v>0.706225199837483</v>
+        <v>0.66762182743057696</v>
       </c>
       <c r="E219">
         <v>1</v>
@@ -11452,16 +11452,16 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B220">
         <v>1</v>
       </c>
       <c r="C220" s="2">
-        <v>0.293192053362474</v>
+        <v>0.33252195344361501</v>
       </c>
       <c r="D220" s="2">
-        <v>0.706807946637525</v>
+        <v>0.66747804655638399</v>
       </c>
       <c r="E220">
         <v>1</v>
@@ -11469,16 +11469,16 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="B221">
         <v>1</v>
       </c>
       <c r="C221" s="2">
-        <v>0.29244533845704701</v>
+        <v>0.33252591512111801</v>
       </c>
       <c r="D221" s="2">
-        <v>0.70755466154295199</v>
+        <v>0.66747408487888105</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -11486,16 +11486,16 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="B222">
         <v>1</v>
       </c>
       <c r="C222" s="2">
-        <v>0.292362884790758</v>
+        <v>0.33290418266782101</v>
       </c>
       <c r="D222" s="2">
-        <v>0.707637115209241</v>
+        <v>0.66709581733217804</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -11503,16 +11503,16 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223">
-        <v>248</v>
+        <v>121</v>
       </c>
       <c r="B223">
         <v>1</v>
       </c>
       <c r="C223" s="2">
-        <v>0.29076737013153298</v>
+        <v>0.33316374142997002</v>
       </c>
       <c r="D223" s="2">
-        <v>0.70923262986846602</v>
+        <v>0.66683625857002904</v>
       </c>
       <c r="E223">
         <v>1</v>
@@ -11520,16 +11520,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224">
-        <v>395</v>
+        <v>217</v>
       </c>
       <c r="B224">
         <v>1</v>
       </c>
       <c r="C224" s="2">
-        <v>0.28951606104317201</v>
+        <v>0.33397925673477202</v>
       </c>
       <c r="D224" s="2">
-        <v>0.71048393895682704</v>
+        <v>0.66602074326522798</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -11537,16 +11537,16 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="B225">
         <v>1</v>
       </c>
       <c r="C225" s="2">
-        <v>0.28923921709920603</v>
+        <v>0.33531155423528902</v>
       </c>
       <c r="D225" s="2">
-        <v>0.71076078290079303</v>
+        <v>0.66468844576470998</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -11554,16 +11554,16 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" s="2">
-        <v>0.28324976745032598</v>
+        <v>0.33683371706656301</v>
       </c>
       <c r="D226" s="2">
-        <v>0.71675023254967296</v>
+        <v>0.66316628293343605</v>
       </c>
       <c r="E226">
         <v>1</v>
@@ -11571,16 +11571,16 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227" s="2">
-        <v>0.28199995822201401</v>
+        <v>0.33953936742927499</v>
       </c>
       <c r="D227" s="2">
-        <v>0.71800004177798504</v>
+        <v>0.66046063257072396</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -11588,16 +11588,16 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228" s="2">
-        <v>0.28119678566501699</v>
+        <v>0.34036807528809898</v>
       </c>
       <c r="D228" s="2">
-        <v>0.71880321433498195</v>
+        <v>0.65963192471190002</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -11605,16 +11605,16 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="B229">
         <v>1</v>
       </c>
       <c r="C229" s="2">
-        <v>0.28063172859399699</v>
+        <v>0.34179201865543501</v>
       </c>
       <c r="D229" s="2">
-        <v>0.71936827140600201</v>
+        <v>0.65820798134456404</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -11622,16 +11622,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230">
-        <v>331</v>
+        <v>199</v>
       </c>
       <c r="B230">
         <v>1</v>
       </c>
       <c r="C230" s="2">
-        <v>0.27781570733417399</v>
+        <v>0.34404270866895897</v>
       </c>
       <c r="D230" s="2">
-        <v>0.72218429266582496</v>
+        <v>0.65595729133103997</v>
       </c>
       <c r="E230">
         <v>1</v>
@@ -11639,16 +11639,16 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231">
-        <v>47</v>
+        <v>366</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C231" s="2">
-        <v>0.27710211064376999</v>
+        <v>0.34966680554516899</v>
       </c>
       <c r="D231" s="2">
-        <v>0.72289788935622901</v>
+        <v>0.65033319445482995</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -11656,16 +11656,16 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="B232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C232" s="2">
-        <v>0.27554670281010102</v>
+        <v>0.35022183900291098</v>
       </c>
       <c r="D232" s="2">
-        <v>0.72445329718989804</v>
+        <v>0.64977816099708796</v>
       </c>
       <c r="E232">
         <v>1</v>
@@ -11673,16 +11673,16 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="B233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C233" s="2">
-        <v>0.27374413181205498</v>
+        <v>0.351634587736596</v>
       </c>
       <c r="D233" s="2">
-        <v>0.72625586818794396</v>
+        <v>0.64836541226340305</v>
       </c>
       <c r="E233">
         <v>1</v>
@@ -11690,16 +11690,16 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B234">
         <v>1</v>
       </c>
       <c r="C234" s="2">
-        <v>0.27318290242094601</v>
+        <v>0.35419913857142499</v>
       </c>
       <c r="D234" s="2">
-        <v>0.726817097579053</v>
+        <v>0.64580086142857396</v>
       </c>
       <c r="E234">
         <v>1</v>
@@ -11707,16 +11707,16 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="B235">
         <v>1</v>
       </c>
       <c r="C235" s="2">
-        <v>0.27253556424993602</v>
+        <v>0.35504389074395398</v>
       </c>
       <c r="D235" s="2">
-        <v>0.72746443575006303</v>
+        <v>0.64495610925604496</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -11724,16 +11724,16 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="B236">
         <v>1</v>
       </c>
       <c r="C236" s="2">
-        <v>0.27158049470731899</v>
+        <v>0.35882112486155499</v>
       </c>
       <c r="D236" s="2">
-        <v>0.72841950529267996</v>
+        <v>0.64117887513844496</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -11741,16 +11741,16 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="B237">
         <v>1</v>
       </c>
       <c r="C237" s="2">
-        <v>0.27063113603419198</v>
+        <v>0.36020230592508801</v>
       </c>
       <c r="D237" s="2">
-        <v>0.72936886396580702</v>
+        <v>0.63979769407491105</v>
       </c>
       <c r="E237">
         <v>1</v>
@@ -11758,16 +11758,16 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238">
-        <v>298</v>
+        <v>129</v>
       </c>
       <c r="B238">
         <v>1</v>
       </c>
       <c r="C238" s="2">
-        <v>0.26898675342452699</v>
+        <v>0.360303582094679</v>
       </c>
       <c r="D238" s="2">
-        <v>0.73101324657547195</v>
+        <v>0.63969641790532095</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -11775,16 +11775,16 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="B239">
         <v>1</v>
       </c>
       <c r="C239" s="2">
-        <v>0.26886434325654102</v>
+        <v>0.360801501137202</v>
       </c>
       <c r="D239" s="2">
-        <v>0.73113565674345804</v>
+        <v>0.639198498862797</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -11792,16 +11792,16 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="B240">
         <v>1</v>
       </c>
       <c r="C240" s="2">
-        <v>0.26495177030531097</v>
+        <v>0.36187059885015399</v>
       </c>
       <c r="D240" s="2">
-        <v>0.73504822969468797</v>
+        <v>0.63812940114984495</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -11809,16 +11809,16 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241">
-        <v>68</v>
+        <v>383</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241" s="2">
-        <v>0.26432012208739603</v>
+        <v>0.36242433927902501</v>
       </c>
       <c r="D241" s="2">
-        <v>0.73567987791260303</v>
+        <v>0.63757566072097405</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -11826,16 +11826,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B242">
         <v>1</v>
       </c>
       <c r="C242" s="2">
-        <v>0.26392854987696102</v>
+        <v>0.36519773535169497</v>
       </c>
       <c r="D242" s="2">
-        <v>0.73607145012303798</v>
+        <v>0.63480226464830403</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -11843,16 +11843,16 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243" s="2">
-        <v>0.26099325252351802</v>
+        <v>0.36717398424111303</v>
       </c>
       <c r="D243" s="2">
-        <v>0.73900674747648099</v>
+        <v>0.63282601575888597</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -11860,16 +11860,16 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244">
-        <v>378</v>
+        <v>214</v>
       </c>
       <c r="B244">
         <v>1</v>
       </c>
       <c r="C244" s="2">
-        <v>0.25941096366542399</v>
+        <v>0.37246639873509901</v>
       </c>
       <c r="D244" s="2">
-        <v>0.74058903633457496</v>
+        <v>0.62753360126489999</v>
       </c>
       <c r="E244">
         <v>1</v>
@@ -11877,16 +11877,16 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245">
-        <v>216</v>
+        <v>2</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C245" s="2">
-        <v>0.258761506146721</v>
+        <v>0.37313482853214602</v>
       </c>
       <c r="D245" s="2">
-        <v>0.741238493853278</v>
+        <v>0.62686517146785303</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -11894,16 +11894,16 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="B246">
         <v>1</v>
       </c>
       <c r="C246" s="2">
-        <v>0.25779861717860603</v>
+        <v>0.37448994398639801</v>
       </c>
       <c r="D246" s="2">
-        <v>0.74220138282139303</v>
+        <v>0.62551005601360199</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -11911,16 +11911,16 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="B247">
         <v>1</v>
       </c>
       <c r="C247" s="2">
-        <v>0.25728858915584601</v>
+        <v>0.37480688782848398</v>
       </c>
       <c r="D247" s="2">
-        <v>0.74271141084415304</v>
+        <v>0.62519311217151496</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -11928,16 +11928,16 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="B248">
         <v>1</v>
       </c>
       <c r="C248" s="2">
-        <v>0.25445357710754901</v>
+        <v>0.37533076811223998</v>
       </c>
       <c r="D248" s="2">
-        <v>0.74554642289244999</v>
+        <v>0.62466923188775902</v>
       </c>
       <c r="E248">
         <v>1</v>
@@ -11945,16 +11945,16 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C249" s="2">
-        <v>0.25358619599469401</v>
+        <v>0.37614659168917403</v>
       </c>
       <c r="D249" s="2">
-        <v>0.74641380400530499</v>
+        <v>0.62385340831082503</v>
       </c>
       <c r="E249">
         <v>1</v>
@@ -11962,16 +11962,16 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C250" s="2">
-        <v>0.251155272837155</v>
+        <v>0.37900338060171501</v>
       </c>
       <c r="D250" s="2">
-        <v>0.748844727162844</v>
+        <v>0.62099661939828399</v>
       </c>
       <c r="E250">
         <v>1</v>
@@ -11979,16 +11979,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="B251">
         <v>1</v>
       </c>
       <c r="C251" s="2">
-        <v>0.25084564556503902</v>
+        <v>0.38145424209809498</v>
       </c>
       <c r="D251" s="2">
-        <v>0.74915435443496003</v>
+        <v>0.61854575790190403</v>
       </c>
       <c r="E251">
         <v>1</v>
@@ -11996,16 +11996,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C252" s="2">
-        <v>0.24920147230790801</v>
+        <v>0.38408044177670497</v>
       </c>
       <c r="D252" s="2">
-        <v>0.75079852769209099</v>
+        <v>0.61591955822329403</v>
       </c>
       <c r="E252">
         <v>1</v>
@@ -12013,16 +12013,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" s="2">
-        <v>0.24738606058746601</v>
+        <v>0.38412705961094001</v>
       </c>
       <c r="D253" s="2">
-        <v>0.75261393941253296</v>
+        <v>0.61587294038905904</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -12030,16 +12030,16 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="B254">
         <v>1</v>
       </c>
       <c r="C254" s="2">
-        <v>0.24688002564640901</v>
+        <v>0.38874413422845</v>
       </c>
       <c r="D254" s="2">
-        <v>0.75311997435359002</v>
+        <v>0.611255865771549</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -12047,16 +12047,16 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C255" s="2">
-        <v>0.245762787463981</v>
+        <v>0.38915530580473101</v>
       </c>
       <c r="D255" s="2">
-        <v>0.75423721253601805</v>
+        <v>0.61084469419526799</v>
       </c>
       <c r="E255">
         <v>1</v>
@@ -12064,16 +12064,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256">
-        <v>230</v>
+        <v>154</v>
       </c>
       <c r="B256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C256" s="2">
-        <v>0.24505919629988099</v>
+        <v>0.38965652511280502</v>
       </c>
       <c r="D256" s="2">
-        <v>0.75494080370011796</v>
+        <v>0.61034347488719398</v>
       </c>
       <c r="E256">
         <v>1</v>
@@ -12081,16 +12081,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C257" s="2">
-        <v>0.24315245187682499</v>
+        <v>0.39271216693817601</v>
       </c>
       <c r="D257" s="2">
-        <v>0.75684754812317401</v>
+        <v>0.60728783306182299</v>
       </c>
       <c r="E257">
         <v>1</v>
@@ -12098,16 +12098,16 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258">
-        <v>172</v>
+        <v>386</v>
       </c>
       <c r="B258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C258" s="2">
-        <v>0.242775916142313</v>
+        <v>0.39290176906390001</v>
       </c>
       <c r="D258" s="2">
-        <v>0.75722408385768603</v>
+        <v>0.60709823093609905</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -12115,16 +12115,16 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="B259">
         <v>1</v>
       </c>
       <c r="C259" s="2">
-        <v>0.241058229569376</v>
+        <v>0.40276566195411301</v>
       </c>
       <c r="D259" s="2">
-        <v>0.75894177043062305</v>
+        <v>0.59723433804588599</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -12132,16 +12132,16 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="B260">
         <v>1</v>
       </c>
       <c r="C260" s="2">
-        <v>0.24004294574812199</v>
+        <v>0.403148640243434</v>
       </c>
       <c r="D260" s="2">
-        <v>0.75995705425187798</v>
+        <v>0.596851359756565</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -12149,16 +12149,16 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="B261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C261" s="2">
-        <v>0.23777838029922499</v>
+        <v>0.40467611180049401</v>
       </c>
       <c r="D261" s="2">
-        <v>0.76222161970077396</v>
+        <v>0.59532388819950499</v>
       </c>
       <c r="E261">
         <v>1</v>
@@ -12166,16 +12166,16 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262">
-        <v>310</v>
+        <v>96</v>
       </c>
       <c r="B262">
         <v>1</v>
       </c>
       <c r="C262" s="2">
-        <v>0.234067189161943</v>
+        <v>0.404889617997508</v>
       </c>
       <c r="D262" s="2">
-        <v>0.76593281083805598</v>
+        <v>0.595110382002491</v>
       </c>
       <c r="E262">
         <v>1</v>
@@ -12183,16 +12183,16 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263">
-        <v>153</v>
+        <v>277</v>
       </c>
       <c r="B263">
         <v>1</v>
       </c>
       <c r="C263" s="2">
-        <v>0.23337679864709401</v>
+        <v>0.406092544147795</v>
       </c>
       <c r="D263" s="2">
-        <v>0.76662320135290596</v>
+        <v>0.59390745585220395</v>
       </c>
       <c r="E263">
         <v>1</v>
@@ -12200,16 +12200,16 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="B264">
         <v>1</v>
       </c>
       <c r="C264" s="2">
-        <v>0.232119132161165</v>
+        <v>0.40677009417979199</v>
       </c>
       <c r="D264" s="2">
-        <v>0.76788086783883402</v>
+        <v>0.59322990582020696</v>
       </c>
       <c r="E264">
         <v>1</v>
@@ -12217,16 +12217,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C265" s="2">
-        <v>0.231983282287378</v>
+        <v>0.40703652695507297</v>
       </c>
       <c r="D265" s="2">
-        <v>0.76801671771262103</v>
+        <v>0.59296347304492603</v>
       </c>
       <c r="E265">
         <v>1</v>
@@ -12234,16 +12234,16 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266">
-        <v>218</v>
+        <v>312</v>
       </c>
       <c r="B266">
         <v>0</v>
       </c>
       <c r="C266" s="2">
-        <v>0.229074471093861</v>
+        <v>0.40983085955818799</v>
       </c>
       <c r="D266" s="2">
-        <v>0.77092552890613897</v>
+        <v>0.59016914044181101</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -12251,16 +12251,16 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267">
-        <v>302</v>
+        <v>361</v>
       </c>
       <c r="B267">
         <v>1</v>
       </c>
       <c r="C267" s="2">
-        <v>0.228282541273229</v>
+        <v>0.41009599632030103</v>
       </c>
       <c r="D267" s="2">
-        <v>0.77171745872677</v>
+        <v>0.58990400367969797</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -12268,16 +12268,16 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268">
-        <v>301</v>
+        <v>26</v>
       </c>
       <c r="B268">
         <v>1</v>
       </c>
       <c r="C268" s="2">
-        <v>0.228181169590225</v>
+        <v>0.41040746297325498</v>
       </c>
       <c r="D268" s="2">
-        <v>0.77181883040977395</v>
+        <v>0.58959253702674397</v>
       </c>
       <c r="E268">
         <v>1</v>
@@ -12285,16 +12285,16 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="B269">
         <v>1</v>
       </c>
       <c r="C269" s="2">
-        <v>0.226095186262498</v>
+        <v>0.41506780110979002</v>
       </c>
       <c r="D269" s="2">
-        <v>0.77390481373750097</v>
+        <v>0.58493219889020898</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -12302,16 +12302,16 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="B270">
         <v>1</v>
       </c>
       <c r="C270" s="2">
-        <v>0.222126658861098</v>
+        <v>0.41692655978883802</v>
       </c>
       <c r="D270" s="2">
-        <v>0.77787334113890105</v>
+        <v>0.58307344021116103</v>
       </c>
       <c r="E270">
         <v>1</v>
@@ -12319,16 +12319,16 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271">
-        <v>380</v>
+        <v>188</v>
       </c>
       <c r="B271">
         <v>1</v>
       </c>
       <c r="C271" s="2">
-        <v>0.221651020308201</v>
+        <v>0.419284441852046</v>
       </c>
       <c r="D271" s="2">
-        <v>0.77834897969179895</v>
+        <v>0.58071555814795295</v>
       </c>
       <c r="E271">
         <v>1</v>
@@ -12336,16 +12336,16 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="B272">
         <v>1</v>
       </c>
       <c r="C272" s="2">
-        <v>0.221082797625095</v>
+        <v>0.41958265785267901</v>
       </c>
       <c r="D272" s="2">
-        <v>0.77891720237490403</v>
+        <v>0.58041734214731999</v>
       </c>
       <c r="E272">
         <v>1</v>
@@ -12353,16 +12353,16 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273">
-        <v>107</v>
+        <v>387</v>
       </c>
       <c r="B273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C273" s="2">
-        <v>0.21920465098860301</v>
+        <v>0.42061007803986</v>
       </c>
       <c r="D273" s="2">
-        <v>0.78079534901139602</v>
+        <v>0.57938992196013905</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -12370,16 +12370,16 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="B274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C274" s="2">
-        <v>0.21891851682114299</v>
+        <v>0.42084065872179399</v>
       </c>
       <c r="D274" s="2">
-        <v>0.78108148317885595</v>
+        <v>0.57915934127820501</v>
       </c>
       <c r="E274">
         <v>1</v>
@@ -12387,16 +12387,16 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C275" s="2">
-        <v>0.218847660579087</v>
+        <v>0.420856120362121</v>
       </c>
       <c r="D275" s="2">
-        <v>0.781152339420912</v>
+        <v>0.57914387963787795</v>
       </c>
       <c r="E275">
         <v>1</v>
@@ -12404,16 +12404,16 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C276" s="2">
-        <v>0.21638057887512099</v>
+        <v>0.42105988515153397</v>
       </c>
       <c r="D276" s="2">
-        <v>0.78361942112487804</v>
+        <v>0.57894011484846497</v>
       </c>
       <c r="E276">
         <v>1</v>
@@ -12421,16 +12421,16 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277">
-        <v>95</v>
+        <v>339</v>
       </c>
       <c r="B277">
         <v>1</v>
       </c>
       <c r="C277" s="2">
-        <v>0.21634993691925999</v>
+        <v>0.42802902753623201</v>
       </c>
       <c r="D277" s="2">
-        <v>0.78365006308073903</v>
+        <v>0.57197097246376705</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -12438,16 +12438,16 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278">
-        <v>362</v>
+        <v>63</v>
       </c>
       <c r="B278">
         <v>1</v>
       </c>
       <c r="C278" s="2">
-        <v>0.21564774482812299</v>
+        <v>0.431198767000112</v>
       </c>
       <c r="D278" s="2">
-        <v>0.78435225517187601</v>
+        <v>0.56880123299988705</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -12455,16 +12455,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B279">
         <v>1</v>
       </c>
       <c r="C279" s="2">
-        <v>0.21418280292561201</v>
+        <v>0.43237789482669697</v>
       </c>
       <c r="D279" s="2">
-        <v>0.78581719707438702</v>
+        <v>0.56762210517330203</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -12472,16 +12472,16 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C280" s="2">
-        <v>0.213201578455189</v>
+        <v>0.43409471053679699</v>
       </c>
       <c r="D280" s="2">
-        <v>0.78679842154480994</v>
+        <v>0.56590528946320195</v>
       </c>
       <c r="E280">
         <v>1</v>
@@ -12489,16 +12489,16 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="B281">
         <v>1</v>
       </c>
       <c r="C281" s="2">
-        <v>0.21123644945783099</v>
+        <v>0.43517222180315002</v>
       </c>
       <c r="D281" s="2">
-        <v>0.78876355054216796</v>
+        <v>0.56482777819684904</v>
       </c>
       <c r="E281">
         <v>1</v>
@@ -12506,16 +12506,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282">
-        <v>250</v>
+        <v>328</v>
       </c>
       <c r="B282">
         <v>1</v>
       </c>
       <c r="C282" s="2">
-        <v>0.209999852324256</v>
+        <v>0.43757778714511097</v>
       </c>
       <c r="D282" s="2">
-        <v>0.790000147675743</v>
+        <v>0.56242221285488803</v>
       </c>
       <c r="E282">
         <v>1</v>
@@ -12523,16 +12523,16 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283">
-        <v>70</v>
+        <v>334</v>
       </c>
       <c r="B283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C283" s="2">
-        <v>0.20754281370403799</v>
+        <v>0.443993155584614</v>
       </c>
       <c r="D283" s="2">
-        <v>0.79245718629596096</v>
+        <v>0.55600684441538495</v>
       </c>
       <c r="E283">
         <v>1</v>
@@ -12540,16 +12540,16 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284">
-        <v>283</v>
+        <v>163</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C284" s="2">
-        <v>0.20026538233142899</v>
+        <v>0.44501333059346398</v>
       </c>
       <c r="D284" s="2">
-        <v>0.79973461766857001</v>
+        <v>0.55498666940653496</v>
       </c>
       <c r="E284">
         <v>1</v>
@@ -12557,16 +12557,16 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="B285">
         <v>1</v>
       </c>
       <c r="C285" s="2">
-        <v>0.20004736023532599</v>
+        <v>0.44999501854929402</v>
       </c>
       <c r="D285" s="2">
-        <v>0.79995263976467301</v>
+        <v>0.55000498145070598</v>
       </c>
       <c r="E285">
         <v>1</v>
@@ -12574,16 +12574,16 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B286">
         <v>1</v>
       </c>
       <c r="C286" s="2">
-        <v>0.19860742269130699</v>
+        <v>0.45414094314373399</v>
       </c>
       <c r="D286" s="2">
-        <v>0.80139257730869196</v>
+        <v>0.54585905685626501</v>
       </c>
       <c r="E286">
         <v>1</v>
@@ -12591,16 +12591,16 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287">
-        <v>72</v>
+        <v>265</v>
       </c>
       <c r="B287">
         <v>1</v>
       </c>
       <c r="C287" s="2">
-        <v>0.196580855402927</v>
+        <v>0.45461313661081898</v>
       </c>
       <c r="D287" s="2">
-        <v>0.80341914459707198</v>
+        <v>0.54538686338917997</v>
       </c>
       <c r="E287">
         <v>1</v>
@@ -12608,16 +12608,16 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288">
-        <v>393</v>
+        <v>220</v>
       </c>
       <c r="B288">
         <v>1</v>
       </c>
       <c r="C288" s="2">
-        <v>0.196165976432077</v>
+        <v>0.45580682132009398</v>
       </c>
       <c r="D288" s="2">
-        <v>0.803834023567922</v>
+        <v>0.54419317867990502</v>
       </c>
       <c r="E288">
         <v>1</v>
@@ -12625,16 +12625,16 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C289" s="2">
-        <v>0.192981801475509</v>
+        <v>0.45837929244292203</v>
       </c>
       <c r="D289" s="2">
-        <v>0.80701819852448997</v>
+        <v>0.54162070755707703</v>
       </c>
       <c r="E289">
         <v>1</v>
@@ -12642,16 +12642,16 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="B290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C290" s="2">
-        <v>0.19250822863575001</v>
+        <v>0.46016692119865099</v>
       </c>
       <c r="D290" s="2">
-        <v>0.80749177136424899</v>
+        <v>0.53983307880134801</v>
       </c>
       <c r="E290">
         <v>1</v>
@@ -12659,16 +12659,16 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291">
-        <v>35</v>
+        <v>315</v>
       </c>
       <c r="B291">
         <v>0</v>
       </c>
       <c r="C291" s="2">
-        <v>0.18906972146261999</v>
+        <v>0.460246149425933</v>
       </c>
       <c r="D291" s="2">
-        <v>0.81093027853737898</v>
+        <v>0.539753850574066</v>
       </c>
       <c r="E291">
         <v>1</v>
@@ -12676,16 +12676,16 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="B292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C292" s="2">
-        <v>0.187990830009645</v>
+        <v>0.460815389856161</v>
       </c>
       <c r="D292" s="2">
-        <v>0.812009169990354</v>
+        <v>0.53918461014383801</v>
       </c>
       <c r="E292">
         <v>1</v>
@@ -12693,16 +12693,16 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293">
-        <v>50</v>
+        <v>397</v>
       </c>
       <c r="B293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293" s="2">
-        <v>0.186834984626019</v>
+        <v>0.46133435036995002</v>
       </c>
       <c r="D293" s="2">
-        <v>0.813165015373981</v>
+        <v>0.53866564963004904</v>
       </c>
       <c r="E293">
         <v>1</v>
@@ -12710,16 +12710,16 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="B294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C294" s="2">
-        <v>0.18539601473359399</v>
+        <v>0.46355419166759299</v>
       </c>
       <c r="D294" s="2">
-        <v>0.81460398526640498</v>
+        <v>0.53644580833240596</v>
       </c>
       <c r="E294">
         <v>1</v>
@@ -12727,16 +12727,16 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B295">
         <v>1</v>
       </c>
       <c r="C295" s="2">
-        <v>0.18485029987608001</v>
+        <v>0.464936477228028</v>
       </c>
       <c r="D295" s="2">
-        <v>0.81514970012391896</v>
+        <v>0.535063522771971</v>
       </c>
       <c r="E295">
         <v>1</v>
@@ -12744,16 +12744,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="B296">
         <v>1</v>
       </c>
       <c r="C296" s="2">
-        <v>0.18479289542483801</v>
+        <v>0.46684649874114398</v>
       </c>
       <c r="D296" s="2">
-        <v>0.81520710457516199</v>
+        <v>0.53315350125885497</v>
       </c>
       <c r="E296">
         <v>1</v>
@@ -12761,16 +12761,16 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297">
-        <v>116</v>
+        <v>360</v>
       </c>
       <c r="B297">
         <v>1</v>
       </c>
       <c r="C297" s="2">
-        <v>0.182977159439841</v>
+        <v>0.47309116483942099</v>
       </c>
       <c r="D297" s="2">
-        <v>0.81702284056015795</v>
+        <v>0.52690883516057796</v>
       </c>
       <c r="E297">
         <v>1</v>
@@ -12778,16 +12778,16 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="B298">
         <v>1</v>
       </c>
       <c r="C298" s="2">
-        <v>0.17775590926644699</v>
+        <v>0.47569637223121702</v>
       </c>
       <c r="D298" s="2">
-        <v>0.82224409073355298</v>
+        <v>0.52430362776878203</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -12795,16 +12795,16 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="B299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C299" s="2">
-        <v>0.17751077104589399</v>
+        <v>0.47736289163957002</v>
       </c>
       <c r="D299" s="2">
-        <v>0.82248922895410503</v>
+        <v>0.52263710836042898</v>
       </c>
       <c r="E299">
         <v>1</v>
@@ -12812,16 +12812,16 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B300">
         <v>0</v>
       </c>
       <c r="C300" s="2">
-        <v>0.17624644158295</v>
+        <v>0.47817569459750597</v>
       </c>
       <c r="D300" s="2">
-        <v>0.823753558417049</v>
+        <v>0.52182430540249303</v>
       </c>
       <c r="E300">
         <v>1</v>
@@ -12829,16 +12829,16 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="B301">
         <v>1</v>
       </c>
       <c r="C301" s="2">
-        <v>0.17563520788711501</v>
+        <v>0.47917879496022198</v>
       </c>
       <c r="D301" s="2">
-        <v>0.82436479211288405</v>
+        <v>0.52082120503977702</v>
       </c>
       <c r="E301">
         <v>1</v>
@@ -12846,16 +12846,16 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302">
-        <v>351</v>
+        <v>239</v>
       </c>
       <c r="B302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C302" s="2">
-        <v>0.17484992424090801</v>
+        <v>0.479211650366479</v>
       </c>
       <c r="D302" s="2">
-        <v>0.82515007575909105</v>
+        <v>0.52078834963352005</v>
       </c>
       <c r="E302">
         <v>1</v>
@@ -12863,16 +12863,16 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="B303">
         <v>1</v>
       </c>
       <c r="C303" s="2">
-        <v>0.17295166446565099</v>
+        <v>0.48293966373122399</v>
       </c>
       <c r="D303" s="2">
-        <v>0.82704833553434798</v>
+        <v>0.51706033626877501</v>
       </c>
       <c r="E303">
         <v>1</v>
@@ -12880,16 +12880,16 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304">
-        <v>213</v>
+        <v>10</v>
       </c>
       <c r="B304">
         <v>1</v>
       </c>
       <c r="C304" s="2">
-        <v>0.172493215668758</v>
+        <v>0.484814554431381</v>
       </c>
       <c r="D304" s="2">
-        <v>0.82750678433124103</v>
+        <v>0.51518544556861801</v>
       </c>
       <c r="E304">
         <v>1</v>
@@ -12897,16 +12897,16 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="B305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C305" s="2">
-        <v>0.172363063204619</v>
+        <v>0.48579403022614398</v>
       </c>
       <c r="D305" s="2">
-        <v>0.82763693679538097</v>
+        <v>0.51420596977385502</v>
       </c>
       <c r="E305">
         <v>1</v>
@@ -12914,16 +12914,16 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B306">
         <v>0</v>
       </c>
       <c r="C306" s="2">
-        <v>0.17013659553534799</v>
+        <v>0.48924707307172799</v>
       </c>
       <c r="D306" s="2">
-        <v>0.82986340446465101</v>
+        <v>0.51075292692827101</v>
       </c>
       <c r="E306">
         <v>1</v>
@@ -12931,16 +12931,16 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="B307">
         <v>1</v>
       </c>
       <c r="C307" s="2">
-        <v>0.16978387567657399</v>
+        <v>0.49115954554803998</v>
       </c>
       <c r="D307" s="2">
-        <v>0.83021612432342495</v>
+        <v>0.50884045445195902</v>
       </c>
       <c r="E307">
         <v>1</v>
@@ -12948,16 +12948,16 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="B308">
         <v>1</v>
       </c>
       <c r="C308" s="2">
-        <v>0.16894138655559199</v>
+        <v>0.492064556855701</v>
       </c>
       <c r="D308" s="2">
-        <v>0.83105861344440801</v>
+        <v>0.50793544314429795</v>
       </c>
       <c r="E308">
         <v>1</v>
@@ -12965,16 +12965,16 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B309">
         <v>0</v>
       </c>
       <c r="C309" s="2">
-        <v>0.16869384867392501</v>
+        <v>0.49893371692821997</v>
       </c>
       <c r="D309" s="2">
-        <v>0.83130615132607399</v>
+        <v>0.50106628307177903</v>
       </c>
       <c r="E309">
         <v>1</v>
@@ -12982,16 +12982,16 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B310">
         <v>1</v>
       </c>
       <c r="C310" s="2">
-        <v>0.16712433999908299</v>
+        <v>0.49996779850686501</v>
       </c>
       <c r="D310" s="2">
-        <v>0.83287566000091595</v>
+        <v>0.50003220149313399</v>
       </c>
       <c r="E310">
         <v>1</v>
@@ -12999,1549 +12999,1549 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B311">
         <v>1</v>
       </c>
       <c r="C311" s="2">
-        <v>0.16698835353001401</v>
+        <v>0.50028208072713698</v>
       </c>
       <c r="D311" s="2">
-        <v>0.83301164646998505</v>
+        <v>0.49971791927286202</v>
       </c>
       <c r="E311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312">
-        <v>345</v>
+        <v>29</v>
       </c>
       <c r="B312">
         <v>1</v>
       </c>
       <c r="C312" s="2">
-        <v>0.16639470142360299</v>
+        <v>0.50151153933103498</v>
       </c>
       <c r="D312" s="2">
-        <v>0.83360529857639598</v>
+        <v>0.49848846066896402</v>
       </c>
       <c r="E312">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="B313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C313" s="2">
-        <v>0.164910788500475</v>
+        <v>0.50387210407711203</v>
       </c>
       <c r="D313" s="2">
-        <v>0.83508921149952398</v>
+        <v>0.49612789592288797</v>
       </c>
       <c r="E313">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314">
-        <v>126</v>
+        <v>322</v>
       </c>
       <c r="B314">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C314" s="2">
-        <v>0.164858029819788</v>
+        <v>0.50677657054531899</v>
       </c>
       <c r="D314" s="2">
-        <v>0.83514197018021097</v>
+        <v>0.49322342945468001</v>
       </c>
       <c r="E314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315" s="2">
-        <v>0.162758664718509</v>
+        <v>0.50713081304568297</v>
       </c>
       <c r="D315" s="2">
-        <v>0.83724133528149003</v>
+        <v>0.49286918695431597</v>
       </c>
       <c r="E315">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C316" s="2">
-        <v>0.16257984272083301</v>
+        <v>0.51089785586324499</v>
       </c>
       <c r="D316" s="2">
-        <v>0.83742015727916597</v>
+        <v>0.48910214413675401</v>
       </c>
       <c r="E316">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B317">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C317" s="2">
-        <v>0.16126414372843301</v>
+        <v>0.51381634828274703</v>
       </c>
       <c r="D317" s="2">
-        <v>0.83873585627156699</v>
+        <v>0.48618365171725197</v>
       </c>
       <c r="E317">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318">
-        <v>266</v>
+        <v>6</v>
       </c>
       <c r="B318">
         <v>1</v>
       </c>
       <c r="C318" s="2">
-        <v>0.158637346655433</v>
+        <v>0.51442454871687004</v>
       </c>
       <c r="D318" s="2">
-        <v>0.84136265334456595</v>
+        <v>0.48557545128312901</v>
       </c>
       <c r="E318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319">
-        <v>148</v>
+        <v>363</v>
       </c>
       <c r="B319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C319" s="2">
-        <v>0.15664168779430901</v>
+        <v>0.51524994677824398</v>
       </c>
       <c r="D319" s="2">
-        <v>0.84335831220569002</v>
+        <v>0.48475005322175502</v>
       </c>
       <c r="E319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="B320">
         <v>1</v>
       </c>
       <c r="C320" s="2">
-        <v>0.155593233054059</v>
+        <v>0.51899216178449803</v>
       </c>
       <c r="D320" s="2">
-        <v>0.84440676694593997</v>
+        <v>0.48100783821550103</v>
       </c>
       <c r="E320">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="B321">
         <v>1</v>
       </c>
       <c r="C321" s="2">
-        <v>0.15468352469237001</v>
+        <v>0.52415741302443397</v>
       </c>
       <c r="D321" s="2">
-        <v>0.84531647530762899</v>
+        <v>0.47584258697556497</v>
       </c>
       <c r="E321">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="B322">
         <v>1</v>
       </c>
       <c r="C322" s="2">
-        <v>0.153928066967398</v>
+        <v>0.52552482761053498</v>
       </c>
       <c r="D322" s="2">
-        <v>0.84607193303260098</v>
+        <v>0.47447517238946402</v>
       </c>
       <c r="E322">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="B323">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C323" s="2">
-        <v>0.15182142614027</v>
+        <v>0.53240914966711295</v>
       </c>
       <c r="D323" s="2">
-        <v>0.84817857385972895</v>
+        <v>0.467590850332886</v>
       </c>
       <c r="E323">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B324">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C324" s="2">
-        <v>0.149106990034095</v>
+        <v>0.53400946481075595</v>
       </c>
       <c r="D324" s="2">
-        <v>0.850893009965904</v>
+        <v>0.46599053518924299</v>
       </c>
       <c r="E324">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="B325">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C325" s="2">
-        <v>0.148766680498265</v>
+        <v>0.53799642141559001</v>
       </c>
       <c r="D325" s="2">
-        <v>0.85123331950173398</v>
+        <v>0.46200357858440899</v>
       </c>
       <c r="E325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B326">
         <v>1</v>
       </c>
       <c r="C326" s="2">
-        <v>0.14627891227098699</v>
+        <v>0.54223416007430103</v>
       </c>
       <c r="D326" s="2">
-        <v>0.85372108772901201</v>
+        <v>0.45776583992569803</v>
       </c>
       <c r="E326">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327">
-        <v>203</v>
+        <v>31</v>
       </c>
       <c r="B327">
         <v>0</v>
       </c>
       <c r="C327" s="2">
-        <v>0.14578443815223799</v>
+        <v>0.54661961512289503</v>
       </c>
       <c r="D327" s="2">
-        <v>0.85421556184776104</v>
+        <v>0.45338038487710403</v>
       </c>
       <c r="E327">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328">
-        <v>9</v>
+        <v>347</v>
       </c>
       <c r="B328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C328" s="2">
-        <v>0.144444899221119</v>
+        <v>0.549494286802094</v>
       </c>
       <c r="D328" s="2">
-        <v>0.85555510077887997</v>
+        <v>0.450505713197905</v>
       </c>
       <c r="E328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B329">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C329" s="2">
-        <v>0.14435823152301699</v>
+        <v>0.54962624187008802</v>
       </c>
       <c r="D329" s="2">
-        <v>0.85564176847698203</v>
+        <v>0.45037375812991098</v>
       </c>
       <c r="E329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="B330">
         <v>0</v>
       </c>
       <c r="C330" s="2">
-        <v>0.14433862793601299</v>
+        <v>0.55328556234154003</v>
       </c>
       <c r="D330" s="2">
-        <v>0.85566137206398596</v>
+        <v>0.44671443765845897</v>
       </c>
       <c r="E330">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331">
-        <v>364</v>
+        <v>15</v>
       </c>
       <c r="B331">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C331" s="2">
-        <v>0.14317247958892301</v>
+        <v>0.55402137857425005</v>
       </c>
       <c r="D331" s="2">
-        <v>0.85682752041107602</v>
+        <v>0.44597862142574901</v>
       </c>
       <c r="E331">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332">
-        <v>274</v>
+        <v>195</v>
       </c>
       <c r="B332">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C332" s="2">
-        <v>0.14086257286939299</v>
+        <v>0.55408984271941697</v>
       </c>
       <c r="D332" s="2">
-        <v>0.85913742713060604</v>
+        <v>0.44591015728058198</v>
       </c>
       <c r="E332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B333">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C333" s="2">
-        <v>0.13865003659863501</v>
+        <v>0.55746729042809795</v>
       </c>
       <c r="D333" s="2">
-        <v>0.86134996340136405</v>
+        <v>0.442532709571901</v>
       </c>
       <c r="E333">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334">
-        <v>85</v>
+        <v>272</v>
       </c>
       <c r="B334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C334" s="2">
-        <v>0.13830757054399101</v>
+        <v>0.55755742041737399</v>
       </c>
       <c r="D334" s="2">
-        <v>0.86169242945600799</v>
+        <v>0.44244257958262501</v>
       </c>
       <c r="E334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335">
-        <v>394</v>
+        <v>120</v>
       </c>
       <c r="B335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C335" s="2">
-        <v>0.135367077456225</v>
+        <v>0.56240842927651002</v>
       </c>
       <c r="D335" s="2">
-        <v>0.864632922543774</v>
+        <v>0.43759157072348898</v>
       </c>
       <c r="E335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="B336">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C336" s="2">
-        <v>0.13509044679975901</v>
+        <v>0.56409911280301706</v>
       </c>
       <c r="D336" s="2">
-        <v>0.86490955320023999</v>
+        <v>0.435900887196982</v>
       </c>
       <c r="E336">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="B337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C337" s="2">
-        <v>0.13460563458031799</v>
+        <v>0.56585200155120496</v>
       </c>
       <c r="D337" s="2">
-        <v>0.86539436541968096</v>
+        <v>0.43414799844879398</v>
       </c>
       <c r="E337">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338">
-        <v>388</v>
+        <v>155</v>
       </c>
       <c r="B338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C338" s="2">
-        <v>0.134462758336855</v>
+        <v>0.56842974929308798</v>
       </c>
       <c r="D338" s="2">
-        <v>0.86553724166314405</v>
+        <v>0.43157025070691102</v>
       </c>
       <c r="E338">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="B339">
         <v>0</v>
       </c>
       <c r="C339" s="2">
-        <v>0.13401507233370399</v>
+        <v>0.569553228035239</v>
       </c>
       <c r="D339" s="2">
-        <v>0.86598492766629498</v>
+        <v>0.43044677196476</v>
       </c>
       <c r="E339">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="B340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C340" s="2">
-        <v>0.132515134311087</v>
+        <v>0.57189629354016902</v>
       </c>
       <c r="D340" s="2">
-        <v>0.86748486568891203</v>
+        <v>0.42810370645982998</v>
       </c>
       <c r="E340">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="B341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C341" s="2">
-        <v>0.13108982553902301</v>
+        <v>0.57251257493956198</v>
       </c>
       <c r="D341" s="2">
-        <v>0.86891017446097596</v>
+        <v>0.42748742506043702</v>
       </c>
       <c r="E341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="B342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C342" s="2">
-        <v>0.130388099956985</v>
+        <v>0.57297449365773701</v>
       </c>
       <c r="D342" s="2">
-        <v>0.86961190004301403</v>
+        <v>0.42702550634226299</v>
       </c>
       <c r="E342">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343">
-        <v>23</v>
+        <v>327</v>
       </c>
       <c r="B343">
         <v>1</v>
       </c>
       <c r="C343" s="2">
-        <v>0.12814770184327301</v>
+        <v>0.57363821820748795</v>
       </c>
       <c r="D343" s="2">
-        <v>0.87185229815672605</v>
+        <v>0.426361781792512</v>
       </c>
       <c r="E343">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="B344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C344" s="2">
-        <v>0.12787577977477699</v>
+        <v>0.581315980488193</v>
       </c>
       <c r="D344" s="2">
-        <v>0.87212422022522196</v>
+        <v>0.418684019511806</v>
       </c>
       <c r="E344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="B345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C345" s="2">
-        <v>0.12522590979151499</v>
+        <v>0.58372538605829905</v>
       </c>
       <c r="D345" s="2">
-        <v>0.87477409020848496</v>
+        <v>0.41627461394170001</v>
       </c>
       <c r="E345">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="B346">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C346" s="2">
-        <v>0.124641159433229</v>
+        <v>0.58668245911982098</v>
       </c>
       <c r="D346" s="2">
-        <v>0.87535884056677005</v>
+        <v>0.41331754088017802</v>
       </c>
       <c r="E346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347">
-        <v>311</v>
+        <v>32</v>
       </c>
       <c r="B347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C347" s="2">
-        <v>0.123798192581082</v>
+        <v>0.58764472458003303</v>
       </c>
       <c r="D347" s="2">
-        <v>0.87620180741891696</v>
+        <v>0.41235527541996603</v>
       </c>
       <c r="E347">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C348" s="2">
-        <v>0.122263799627587</v>
+        <v>0.58857271255664101</v>
       </c>
       <c r="D348" s="2">
-        <v>0.87773620037241196</v>
+        <v>0.41142728744335799</v>
       </c>
       <c r="E348">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349">
-        <v>185</v>
+        <v>365</v>
       </c>
       <c r="B349">
         <v>0</v>
       </c>
       <c r="C349" s="2">
-        <v>0.121533068769257</v>
+        <v>0.59699831635998601</v>
       </c>
       <c r="D349" s="2">
-        <v>0.87846693123074204</v>
+        <v>0.40300168364001299</v>
       </c>
       <c r="E349">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B350">
         <v>1</v>
       </c>
       <c r="C350" s="2">
-        <v>0.11888060067003201</v>
+        <v>0.59835038011520503</v>
       </c>
       <c r="D350" s="2">
-        <v>0.88111939932996697</v>
+        <v>0.40164961988479497</v>
       </c>
       <c r="E350">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="B351">
         <v>0</v>
       </c>
       <c r="C351" s="2">
-        <v>0.118420113216181</v>
+        <v>0.60165637151364404</v>
       </c>
       <c r="D351" s="2">
-        <v>0.88157988678381805</v>
+        <v>0.39834362848635502</v>
       </c>
       <c r="E351">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B352">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C352" s="2">
-        <v>0.117609338436776</v>
+        <v>0.60562783860859004</v>
       </c>
       <c r="D352" s="2">
-        <v>0.88239066156322299</v>
+        <v>0.39437216139140902</v>
       </c>
       <c r="E352">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353">
-        <v>140</v>
+        <v>399</v>
       </c>
       <c r="B353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C353" s="2">
-        <v>0.117280992114618</v>
+        <v>0.61225365250215802</v>
       </c>
       <c r="D353" s="2">
-        <v>0.88271900788538105</v>
+        <v>0.38774634749784098</v>
       </c>
       <c r="E353">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="B354">
         <v>0</v>
       </c>
       <c r="C354" s="2">
-        <v>0.116923082189252</v>
+        <v>0.61727408366533698</v>
       </c>
       <c r="D354" s="2">
-        <v>0.88307691781074704</v>
+        <v>0.38272591633466202</v>
       </c>
       <c r="E354">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355">
-        <v>204</v>
+        <v>329</v>
       </c>
       <c r="B355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C355" s="2">
-        <v>0.11670704173786001</v>
+        <v>0.61796354702745404</v>
       </c>
       <c r="D355" s="2">
-        <v>0.88329295826213905</v>
+        <v>0.38203645297254502</v>
       </c>
       <c r="E355">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="B356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C356" s="2">
-        <v>0.115073327708979</v>
+        <v>0.61914961331369101</v>
       </c>
       <c r="D356" s="2">
-        <v>0.88492667229101996</v>
+        <v>0.380850386686308</v>
       </c>
       <c r="E356">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357">
-        <v>221</v>
+        <v>41</v>
       </c>
       <c r="B357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C357" s="2">
-        <v>0.114818543076169</v>
+        <v>0.62488082507515696</v>
       </c>
       <c r="D357" s="2">
-        <v>0.88518145692382999</v>
+        <v>0.37511917492484198</v>
       </c>
       <c r="E357">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358">
-        <v>168</v>
+        <v>389</v>
       </c>
       <c r="B358">
         <v>0</v>
       </c>
       <c r="C358" s="2">
-        <v>0.11474333455334999</v>
+        <v>0.62624388458754698</v>
       </c>
       <c r="D358" s="2">
-        <v>0.88525666544664905</v>
+        <v>0.37375611541245202</v>
       </c>
       <c r="E358">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359">
-        <v>396</v>
+        <v>3</v>
       </c>
       <c r="B359">
         <v>0</v>
       </c>
       <c r="C359" s="2">
-        <v>0.113932462611348</v>
+        <v>0.62976815584399404</v>
       </c>
       <c r="D359" s="2">
-        <v>0.88606753738865096</v>
+        <v>0.37023184415600502</v>
       </c>
       <c r="E359">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360">
-        <v>76</v>
+        <v>267</v>
       </c>
       <c r="B360">
         <v>1</v>
       </c>
       <c r="C360" s="2">
-        <v>0.11366976429652299</v>
+        <v>0.63542216780036598</v>
       </c>
       <c r="D360" s="2">
-        <v>0.88633023570347602</v>
+        <v>0.36457783219963302</v>
       </c>
       <c r="E360">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="B361">
         <v>0</v>
       </c>
       <c r="C361" s="2">
-        <v>0.11363577711256199</v>
+        <v>0.64118633775858003</v>
       </c>
       <c r="D361" s="2">
-        <v>0.88636422288743699</v>
+        <v>0.35881366224141897</v>
       </c>
       <c r="E361">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="B362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C362" s="2">
-        <v>0.112465090885733</v>
+        <v>0.65194753076888401</v>
       </c>
       <c r="D362" s="2">
-        <v>0.88753490911426602</v>
+        <v>0.34805246923111499</v>
       </c>
       <c r="E362">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363">
-        <v>33</v>
+        <v>288</v>
       </c>
       <c r="B363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C363" s="2">
-        <v>0.11154210066959699</v>
+        <v>0.65339672797952197</v>
       </c>
       <c r="D363" s="2">
-        <v>0.88845789933040198</v>
+        <v>0.34660327202047703</v>
       </c>
       <c r="E363">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="B364">
         <v>1</v>
       </c>
       <c r="C364" s="2">
-        <v>0.11004715587545599</v>
+        <v>0.65647768033153198</v>
       </c>
       <c r="D364" s="2">
-        <v>0.88995284412454301</v>
+        <v>0.34352231966846702</v>
       </c>
       <c r="E364">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="B365">
         <v>0</v>
       </c>
       <c r="C365" s="2">
-        <v>0.11000390642123201</v>
+        <v>0.65950496640613998</v>
       </c>
       <c r="D365" s="2">
-        <v>0.88999609357876697</v>
+        <v>0.34049503359385902</v>
       </c>
       <c r="E365">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B366">
         <v>1</v>
       </c>
       <c r="C366" s="2">
-        <v>0.108488790967656</v>
+        <v>0.65975580911763299</v>
       </c>
       <c r="D366" s="2">
-        <v>0.89151120903234304</v>
+        <v>0.34024419088236602</v>
       </c>
       <c r="E366">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367">
-        <v>392</v>
+        <v>143</v>
       </c>
       <c r="B367">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C367" s="2">
-        <v>0.108165510067983</v>
+        <v>0.66650289179223299</v>
       </c>
       <c r="D367" s="2">
-        <v>0.89183448993201597</v>
+        <v>0.33349710820776601</v>
       </c>
       <c r="E367">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B368">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C368" s="2">
-        <v>0.107358052943587</v>
+        <v>0.66865401022957904</v>
       </c>
       <c r="D368" s="2">
-        <v>0.89264194705641298</v>
+        <v>0.33134598977042001</v>
       </c>
       <c r="E368">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="B369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C369" s="2">
-        <v>0.107324056404802</v>
+        <v>0.67682613641658396</v>
       </c>
       <c r="D369" s="2">
-        <v>0.89267594359519697</v>
+        <v>0.32317386358341499</v>
       </c>
       <c r="E369">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="B370">
         <v>1</v>
       </c>
       <c r="C370" s="2">
-        <v>0.102903754003495</v>
+        <v>0.68039890368967304</v>
       </c>
       <c r="D370" s="2">
-        <v>0.89709624599650395</v>
+        <v>0.31960109631032602</v>
       </c>
       <c r="E370">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371">
-        <v>340</v>
+        <v>43</v>
       </c>
       <c r="B371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C371" s="2">
-        <v>0.101896343794128</v>
+        <v>0.68414390250879997</v>
       </c>
       <c r="D371" s="2">
-        <v>0.89810365620587096</v>
+        <v>0.31585609749119897</v>
       </c>
       <c r="E371">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="B372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C372" s="2">
-        <v>0.100761668496054</v>
+        <v>0.68912603776733605</v>
       </c>
       <c r="D372" s="2">
-        <v>0.89923833150394505</v>
+        <v>0.310873962232663</v>
       </c>
       <c r="E372">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="B373">
         <v>0</v>
       </c>
       <c r="C373" s="2">
-        <v>0.100125151845101</v>
+        <v>0.69092089518739497</v>
       </c>
       <c r="D373" s="2">
-        <v>0.89987484815489804</v>
+        <v>0.30907910481260398</v>
       </c>
       <c r="E373">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="B374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C374" s="2">
-        <v>9.9194297389389702E-2</v>
+        <v>0.69551089254609799</v>
       </c>
       <c r="D374" s="2">
-        <v>0.90080570261060999</v>
+        <v>0.30448910745390101</v>
       </c>
       <c r="E374">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="B375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C375" s="2">
-        <v>9.9027356285356596E-2</v>
+        <v>0.69629452308208795</v>
       </c>
       <c r="D375" s="2">
-        <v>0.90097264371464303</v>
+        <v>0.303705476917911</v>
       </c>
       <c r="E375">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376">
-        <v>152</v>
+        <v>344</v>
       </c>
       <c r="B376">
         <v>0</v>
       </c>
       <c r="C376" s="2">
-        <v>9.6431120277745905E-2</v>
+        <v>0.69665244823072903</v>
       </c>
       <c r="D376" s="2">
-        <v>0.90356887972225397</v>
+        <v>0.30334755176926997</v>
       </c>
       <c r="E376">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377">
-        <v>372</v>
+        <v>151</v>
       </c>
       <c r="B377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C377" s="2">
-        <v>9.4369067031179907E-2</v>
+        <v>0.69769425226210302</v>
       </c>
       <c r="D377" s="2">
-        <v>0.90563093296882002</v>
+        <v>0.30230574773789598</v>
       </c>
       <c r="E377">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="B378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C378" s="2">
-        <v>9.3970191702778594E-2</v>
+        <v>0.69788228181596701</v>
       </c>
       <c r="D378" s="2">
-        <v>0.90602980829722102</v>
+        <v>0.30211771818403199</v>
       </c>
       <c r="E378">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="B379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C379" s="2">
-        <v>9.3575518763545598E-2</v>
+        <v>0.69867962252586402</v>
       </c>
       <c r="D379" s="2">
-        <v>0.90642448123645403</v>
+        <v>0.30132037747413498</v>
       </c>
       <c r="E379">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B380">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C380" s="2">
-        <v>9.2925509080634794E-2</v>
+        <v>0.70495768466030795</v>
       </c>
       <c r="D380" s="2">
-        <v>0.90707449091936498</v>
+        <v>0.295042315339691</v>
       </c>
       <c r="E380">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C381" s="2">
-        <v>9.0384901900281395E-2</v>
+        <v>0.70668992579615797</v>
       </c>
       <c r="D381" s="2">
-        <v>0.90961509809971797</v>
+        <v>0.29331007420384198</v>
       </c>
       <c r="E381">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="B382">
         <v>0</v>
       </c>
       <c r="C382" s="2">
-        <v>8.7827184360941904E-2</v>
+        <v>0.70820036920719098</v>
       </c>
       <c r="D382" s="2">
-        <v>0.91217281563905805</v>
+        <v>0.29179963079280802</v>
       </c>
       <c r="E382">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383">
-        <v>336</v>
+        <v>62</v>
       </c>
       <c r="B383">
         <v>1</v>
       </c>
       <c r="C383" s="2">
-        <v>8.6372432368955601E-2</v>
+        <v>0.70994477938834299</v>
       </c>
       <c r="D383" s="2">
-        <v>0.91362756763104402</v>
+        <v>0.29005522061165601</v>
       </c>
       <c r="E383">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="B384">
         <v>1</v>
       </c>
       <c r="C384" s="2">
-        <v>8.5862274993122004E-2</v>
+        <v>0.71976402939073203</v>
       </c>
       <c r="D384" s="2">
-        <v>0.91413772500687795</v>
+        <v>0.28023597060926703</v>
       </c>
       <c r="E384">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B385">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C385" s="2">
-        <v>8.4669761835666199E-2</v>
+        <v>0.720072153616232</v>
       </c>
       <c r="D385" s="2">
-        <v>0.91533023816433301</v>
+        <v>0.279927846383767</v>
       </c>
       <c r="E385">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="B386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C386" s="2">
-        <v>8.4544949832619398E-2</v>
+        <v>0.72274873403993301</v>
       </c>
       <c r="D386" s="2">
-        <v>0.91545505016738005</v>
+        <v>0.277251265960066</v>
       </c>
       <c r="E386">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387">
-        <v>379</v>
+        <v>264</v>
       </c>
       <c r="B387">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C387" s="2">
-        <v>8.4025489097265205E-2</v>
+        <v>0.72339284582967001</v>
       </c>
       <c r="D387" s="2">
-        <v>0.91597451090273396</v>
+        <v>0.27660715417032899</v>
       </c>
       <c r="E387">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="B388">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C388" s="2">
-        <v>8.1077552855233104E-2</v>
+        <v>0.74440235035125202</v>
       </c>
       <c r="D388" s="2">
-        <v>0.91892244714476601</v>
+        <v>0.25559764964874698</v>
       </c>
       <c r="E388">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389">
-        <v>354</v>
+        <v>16</v>
       </c>
       <c r="B389">
         <v>1</v>
       </c>
       <c r="C389" s="2">
-        <v>7.6682959601266004E-2</v>
+        <v>0.74606387404385499</v>
       </c>
       <c r="D389" s="2">
-        <v>0.92331704039873397</v>
+        <v>0.25393612595614401</v>
       </c>
       <c r="E389">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390">
-        <v>276</v>
+        <v>181</v>
       </c>
       <c r="B390">
         <v>0</v>
       </c>
       <c r="C390" s="2">
-        <v>7.3868210807919998E-2</v>
+        <v>0.75312170932141098</v>
       </c>
       <c r="D390" s="2">
-        <v>0.92613178919207995</v>
+        <v>0.24687829067858799</v>
       </c>
       <c r="E390">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391">
-        <v>352</v>
+        <v>234</v>
       </c>
       <c r="B391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C391" s="2">
-        <v>6.8460558867534105E-2</v>
+        <v>0.75672824354326695</v>
       </c>
       <c r="D391" s="2">
-        <v>0.93153944113246501</v>
+        <v>0.24327175645673199</v>
       </c>
       <c r="E391">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="B392">
         <v>0</v>
       </c>
       <c r="C392" s="2">
-        <v>6.7753473930911898E-2</v>
+        <v>0.75702518889234005</v>
       </c>
       <c r="D392" s="2">
-        <v>0.93224652606908798</v>
+        <v>0.24297481110765901</v>
       </c>
       <c r="E392">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="B393">
         <v>0</v>
       </c>
       <c r="C393" s="2">
-        <v>6.6907890345421397E-2</v>
+        <v>0.76025575181913996</v>
       </c>
       <c r="D393" s="2">
-        <v>0.93309210965457801</v>
+        <v>0.23974424818085899</v>
       </c>
       <c r="E393">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394">
-        <v>309</v>
+        <v>105</v>
       </c>
       <c r="B394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C394" s="2">
-        <v>6.5327856328408596E-2</v>
+        <v>0.76031332844253696</v>
       </c>
       <c r="D394" s="2">
-        <v>0.93467214367159102</v>
+        <v>0.23968667155746201</v>
       </c>
       <c r="E394">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="B395">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C395" s="2">
-        <v>6.5322544728043996E-2</v>
+        <v>0.765516263403206</v>
       </c>
       <c r="D395" s="2">
-        <v>0.934677455271956</v>
+        <v>0.234483736596793</v>
       </c>
       <c r="E395">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396">
-        <v>114</v>
+        <v>356</v>
       </c>
       <c r="B396">
         <v>1</v>
       </c>
       <c r="C396" s="2">
-        <v>6.4694371178253898E-2</v>
+        <v>0.76663505665523601</v>
       </c>
       <c r="D396" s="2">
-        <v>0.93530562882174595</v>
+        <v>0.23336494334476299</v>
       </c>
       <c r="E396">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397">
-        <v>286</v>
+        <v>52</v>
       </c>
       <c r="B397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C397" s="2">
-        <v>6.0548217203128397E-2</v>
+        <v>0.76692651002603096</v>
       </c>
       <c r="D397" s="2">
-        <v>0.93945178279687103</v>
+        <v>0.23307348997396801</v>
       </c>
       <c r="E397">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398">
-        <v>245</v>
+        <v>7</v>
       </c>
       <c r="B398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C398" s="2">
-        <v>5.7445627964969201E-2</v>
+        <v>0.77347535673464496</v>
       </c>
       <c r="D398" s="2">
-        <v>0.94255437203503001</v>
+        <v>0.22652464326535399</v>
       </c>
       <c r="E398">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399">
-        <v>44</v>
+        <v>341</v>
       </c>
       <c r="B399">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C399" s="2">
-        <v>5.5949471568144303E-2</v>
+        <v>0.80794744749740299</v>
       </c>
       <c r="D399" s="2">
-        <v>0.944050528431855</v>
+        <v>0.19205255250259601</v>
       </c>
       <c r="E399">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="B400">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C400" s="2">
-        <v>4.6918077701862099E-2</v>
+        <v>0.82158174384212701</v>
       </c>
       <c r="D400" s="2">
-        <v>0.95308192229813704</v>
+        <v>0.17841825615787199</v>
       </c>
       <c r="E400">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B401">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C401" s="2">
-        <v>4.6779713268150502E-2</v>
+        <v>0.82503400713532005</v>
       </c>
       <c r="D401" s="2">
-        <v>0.953220286731849</v>
+        <v>0.17496599286467901</v>
       </c>
       <c r="E401">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/result_analysis/analysis.xlsx
+++ b/result_analysis/analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tintin/Desktop/Projects/credit_risk_model/result_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8831DDB9-1849-5340-962D-71CBF2B20E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B792EA5-9AF6-E945-B565-DA255D487101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="800" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{61FC1A9A-6CB0-D841-9DA7-4D6ECF9C438C}"/>
   </bookViews>
@@ -269,21 +269,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill>
@@ -390,6 +376,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC90F19"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -399,6 +390,1531 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Maximize</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Profit against Predicted Probability of Default</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Total Profit</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6">
+                          <a:lumMod val="75000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-079E-F44A-B5E1-B670670C29C0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>pivot_table!$D$4:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.17496599286467901</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.35881366224141897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.47584258697556497</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.56482777819684904</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63757566072097405</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.68823276453429405</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.73607145012303798</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.790000147675743</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.84607193303260098</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.88753490911426602</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot_table!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-29800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-60000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-88800</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-116200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-146400</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-173800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-201200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-079E-F44A-B5E1-B670670C29C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="907705135"/>
+        <c:axId val="907707743"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="907705135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Model Predicted Probability of Default</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.37937524573177817"/>
+              <c:y val="0.90743766329059639"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="907707743"/>
+        <c:crossesAt val="-250000"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="907707743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="907705135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1174814</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>42269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>538480</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>142713</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04606F60-F557-0424-0946-48AA077DEE4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4137,7 +5653,7 @@
     <dataField name="Min of Probability_Default" fld="3" subtotal="min" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4149,7 +5665,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4179,7 +5695,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}" name="Table1" displayName="Table1" ref="A1:G401" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}" name="Table1" displayName="Table1" ref="A1:G401" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="A1:G401" xr:uid="{00A61614-C026-F049-8D7D-B2C5D987FC7D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E401">
     <sortCondition descending="1" ref="D1:D401"/>
@@ -4187,13 +5703,13 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A33D2E8F-C4FE-744C-B6EA-6D08D082939C}" name="index"/>
     <tableColumn id="2" xr3:uid="{B6ED8025-A452-0545-83F5-078527E9E23D}" name="Actual Outcome"/>
-    <tableColumn id="3" xr3:uid="{482B43F2-766E-4344-A44D-179FE0BFAA6E}" name="Probability_Safe" dataDxfId="11" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{797E6CBE-CC91-DD44-BA30-CDAD50AEEDE6}" name="Probability_Default" dataDxfId="10" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{482B43F2-766E-4344-A44D-179FE0BFAA6E}" name="Probability_Safe" dataDxfId="9" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{797E6CBE-CC91-DD44-BA30-CDAD50AEEDE6}" name="Probability_Default" dataDxfId="8" dataCellStyle="Percent"/>
     <tableColumn id="5" xr3:uid="{8F649A08-FC6F-404F-ADA2-2B66671FF421}" name="Predicted Outcome"/>
-    <tableColumn id="8" xr3:uid="{B81D5698-9F0B-9B45-A8E1-F4463C47F39B}" name="True Positive" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{B81D5698-9F0B-9B45-A8E1-F4463C47F39B}" name="True Positive" dataDxfId="5">
       <calculatedColumnFormula>IF(AND(Table1[[#This Row],[Predicted Outcome]]=1,Table1[[#This Row],[Actual Outcome]]=1),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{47E82062-EA15-D14E-9771-A0661A0DD882}" name="Decile" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{47E82062-EA15-D14E-9771-A0661A0DD882}" name="Decile" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(MAX(IF(Table2[Probability_Default]&lt;Table1[[#This Row],[Probability_Default]],Table2[Probability_Default])),Table2[Probability_Default],Table2[Decile],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4206,7 +5722,7 @@
   <autoFilter ref="J1:K10" xr:uid="{67FE4D2D-295A-FD43-B1A1-4828D3A56142}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{85908CF2-458E-DC4E-9C8D-DD7ACB04BE26}" name="Decile"/>
-    <tableColumn id="2" xr3:uid="{829CD0D6-0304-6044-B4C2-6E080E4914FE}" name="Probability_Default" dataDxfId="9" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{829CD0D6-0304-6044-B4C2-6E080E4914FE}" name="Probability_Default" dataDxfId="7" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4237,16 +5753,16 @@
     <tableColumn id="3" xr3:uid="{4DF9A59C-7522-3B4F-9E93-B8FD4567A10D}" name="Cumulative Defaults">
       <calculatedColumnFormula>SUM($C$4:C4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0B23C047-C32D-3A4B-BD60-B8C615AA7BB4}" name="Cumulative % of Defaults" dataDxfId="6" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0B23C047-C32D-3A4B-BD60-B8C615AA7BB4}" name="Cumulative % of Defaults" dataDxfId="4" dataCellStyle="Percent">
       <calculatedColumnFormula>(H4)/$H$13</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F7D20E3F-556C-1940-82F2-43B673E2D5D4}" name="Cumulative Safe Loans">
       <calculatedColumnFormula>SUM($G$4:G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{828E05FA-42DB-2D44-82BC-3CE97F0BCB66}" name="Cumulative % of Safe Loans" dataDxfId="5" dataCellStyle="Percent">
+    <tableColumn id="6" xr3:uid="{828E05FA-42DB-2D44-82BC-3CE97F0BCB66}" name="Cumulative % of Safe Loans" dataDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>(J4)/$J$13</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B38B3630-1B13-C646-85B9-356D48FF1C8B}" name="Total Profit" dataDxfId="4" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{B38B3630-1B13-C646-85B9-356D48FF1C8B}" name="Total Profit" dataDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[Cumulative Safe Loans]]*$I$18-Table3[[#This Row],[Cumulative Defaults]]*$I$17</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -23245,8 +24761,9 @@
     <mergeCell ref="G18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>